--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,42 +1024,42 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1995498.4</t>
+          <t>2443380.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1183171.94</t>
+          <t>1233866.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>223952.94</v>
+        <v>326866.16</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>210.228</t>
+          <t>42.716</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,42 +1455,42 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-68.41</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1971587.4</t>
+          <t>1995498.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1383171.1</t>
+          <t>1447308.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1209715.2</t>
+          <t>1183171.94</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>588416</t>
+          <t>548190</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>21396.27799944613</t>
+          <t>52558.84065871156</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>330373.73</v>
+        <v>223952.94</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>210.228</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.04</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1097188.6</t>
+          <t>1971587.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1002558.1</t>
+          <t>1383171.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1151381.24</t>
+          <t>1209715.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>94630</t>
+          <t>588416</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-34781.43987228681</t>
+          <t>21396.27799944613</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>21726.9</v>
+        <v>330373.73</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,42 +2171,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>68.61</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-3.49</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>28.002</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2302,72 +2302,72 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-26.97</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.07</t>
+          <t>-103.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>699699.0</t>
+          <t>1724881.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>902862.4</t>
+          <t>1097188.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>908805.3</t>
+          <t>1002558.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1262902.06</t>
+          <t>1151381.24</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5942</t>
+          <t>94630</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-45055.68381211576</t>
+          <t>-34781.43987228681</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-42950.34</v>
+        <v>21726.9</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>50.125</t>
+          <t>28.002</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2758,17 +2758,17 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-39.78</t>
+          <t>-26.97</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.87</t>
+          <t>-103.07</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1254915.0</t>
+          <t>699699.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>939932.6</t>
+          <t>902862.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>906688.0</t>
+          <t>908805.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1280505.3</t>
+          <t>1262902.06</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>-5942</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-45438.47287292028</t>
+          <t>-45055.68381211576</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-23971.54</v>
+        <v>-42950.34</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>37.399</t>
+          <t>50.125</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,32 +3164,32 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3214,22 +3214,22 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-58.11</t>
+          <t>-39.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-102.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>934682.0</t>
+          <t>1254915.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>899118.2</t>
+          <t>939932.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>945049.3</t>
+          <t>906688.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1319081.6</t>
+          <t>1280505.3</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-45931</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-49341.55158763187</t>
+          <t>-45438.47287292028</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-55490.26</v>
+        <v>-23971.54</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>34.748</t>
+          <t>37.399</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,79 +3595,79 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>25.03</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>25.17</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>25.28</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-58.11</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.04</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>25.19</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>25.29</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>24.93</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-69.68</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.21</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>871766.0</t>
+          <t>934682.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>794754.8</t>
+          <t>899118.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>979822.2</t>
+          <t>945049.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1367719.62</t>
+          <t>1319081.6</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>-45931</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-48223.60371391037</t>
+          <t>-49341.55158763187</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-64224.54</v>
+        <v>-55490.26</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>25.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>25.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>34.748</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-18.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,52 +4026,52 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-99.33</t>
+          <t>-69.68</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.82</t>
+          <t>-102.21</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>753250.0</t>
+          <t>871766.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>907927.6</t>
+          <t>794754.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1067569.3</t>
+          <t>979822.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1387727.28</t>
+          <t>1367719.62</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-159641</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-45314.34237515743</t>
+          <t>-48223.60371391037</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-67667.34</v>
+        <v>-64224.54</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,22 +4224,22 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>12.32</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35.302</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.94</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,67 +4457,67 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>25.29</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-178.18</t>
+          <t>-99.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.82</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>885050.0</t>
+          <t>753250.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>914748.2</t>
+          <t>907927.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1050650.7</t>
+          <t>1067569.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1426103.62</t>
+          <t>1387727.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-135902</t>
+          <t>-159641</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-41250.1601028585</t>
+          <t>-45314.34237515743</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-57470.8</v>
+        <v>-67667.34</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>35.302</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-12.94</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4888,67 +4888,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-375.04</t>
+          <t>-178.18</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.76</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1050843.0</t>
+          <t>885050.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>873443.4</t>
+          <t>914748.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1049354.7</t>
+          <t>1050650.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1428606.16</t>
+          <t>1426103.62</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-175911</t>
+          <t>-135902</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-38300.95243717273</t>
+          <t>-41250.1601028585</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-54973.21</v>
+        <v>-57470.8</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,99 +5188,99 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>42.05</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>16.452</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-16.76</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-2.24</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-5.53</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
           <t>25.26</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5280.45</t>
+          <t>-375.04</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.05</t>
+          <t>-100.76</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11954817.74883721</t>
+          <t>11944425.59674923</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>412865.0</t>
+          <t>1050843.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>990980.4</t>
+          <t>873443.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1049025.6</t>
+          <t>1049354.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1421245.26</t>
+          <t>1428606.16</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-58045</t>
+          <t>-175911</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-35269.63238169335</t>
+          <t>-38300.95243717273</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-67205.42999999999</v>
+        <v>-54973.21</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,22 +5517,22 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>12.32</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-28.52</t>
+          <t>-27.01</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,37 +5770,37 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.35</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>13402.8</t>
+          <t>13502.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>28099.9</t>
+          <t>25275.3</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-473.08</v>
+        <v>-1059.74</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-28.76</t>
+          <t>-28.52</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,37 +6201,37 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.04</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>52.81</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-29.28</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-124.89</t>
+          <t>-126.86</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>13127.2</t>
+          <t>13402.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18427.5</t>
+          <t>18750.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>31635.06</t>
+          <t>28099.9</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-5300</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-575.2561739766202</t>
+          <t>-559.5370652281069</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-377.96</v>
+        <v>-473.08</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-22.77</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-28.76</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.14</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,64 +6627,64 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>-0.79</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-124.89</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>15436.0</t>
+          <t>13127.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>19028.5</t>
+          <t>18427.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>32867.0</t>
+          <t>31635.06</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-3592</t>
+          <t>-5300</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-611.1283719113699</t>
+          <t>-575.2561739766202</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-81.79000000000001</v>
+        <v>-377.96</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-21.12</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-16.14</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,17 +7058,17 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -7078,42 +7078,42 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.81</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>11478.0</t>
+          <t>20848.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19367.4</t>
+          <t>15436.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18899.4</t>
+          <t>19028.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>33340.5</t>
+          <t>32867.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-3592</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-707.3726211353406</t>
+          <t>-611.1283719113699</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-477.44</v>
+        <v>-81.79000000000001</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-21.12</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-7.03</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,57 +7474,57 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>53.34</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-124.61</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6960.0</t>
+          <t>11478.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>23495.6</t>
+          <t>19367.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18605.3</t>
+          <t>18899.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>34041.78</t>
+          <t>33340.5</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-749.1791258508009</t>
+          <t>-707.3726211353406</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-21.67</v>
+        <v>-477.44</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-17.00</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>259.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-8.76</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,57 +7905,57 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>63.34</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>51.42</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>53.34</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-124.61</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>13171.0</t>
+          <t>6960.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>24099.0</t>
+          <t>23495.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>19135.7</t>
+          <t>18605.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>34590.34</t>
+          <t>34041.78</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-881.4528072961443</t>
+          <t>-749.1791258508009</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>1114.26</v>
+        <v>-21.67</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-17.16</t>
+          <t>-17.00</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,12 +8093,12 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>480.0</t>
+          <t>259.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,57 +8336,57 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-129.04</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>24723.0</t>
+          <t>13171.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>23727.8</t>
+          <t>24099.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18741.0</t>
+          <t>19135.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>35788.92</t>
+          <t>34590.34</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-1244.309966990364</t>
+          <t>-881.4528072961443</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>2031.77</v>
+        <v>1114.26</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-17.16</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>754.0</t>
+          <t>480.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-10.7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>26.61</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.46</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>93.06</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>51.64</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>50.54</t>
+          <t>50.48</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>53.78</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.81</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-129.04</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>40505.0</t>
+          <t>24723.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>22621.0</t>
+          <t>23727.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>17398.2</t>
+          <t>18741.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>35945.06</t>
+          <t>35788.92</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1839.960353031046</t>
+          <t>-1244.309966990364</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>2032.21</v>
+        <v>2031.77</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>605.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-13.95</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>93.06</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>51.08</t>
+          <t>51.64</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>50.53</t>
+          <t>50.54</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>53.78</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>53.76</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-136.39</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>32119.0</t>
+          <t>40505.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>18431.4</t>
+          <t>22621.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13998.9</t>
+          <t>17398.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>35870.44</t>
+          <t>35945.06</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2543.991694015614</t>
+          <t>-1839.960353031046</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>269.34</v>
+        <v>2032.21</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9386,12 +9386,12 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>605.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-13.95</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>51.08</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>50.53</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>53.99</t>
+          <t>53.88</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>53.74</t>
+          <t>53.76</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-139.68</t>
+          <t>-136.39</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9977.0</t>
+          <t>32119.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>13715.0</t>
+          <t>18431.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11377.1</t>
+          <t>13998.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>36959.5</t>
+          <t>35870.44</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-3055.506542605452</t>
+          <t>-2543.991694015614</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-1360.17</v>
+        <v>269.34</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-16.01</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.91</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.40</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>50.36</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.57</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>54.11</t>
+          <t>53.99</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>53.74</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>16.37</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-141.82</t>
+          <t>-139.68</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>100241.5194805195</t>
+          <t>100113.196685879</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>11315.0</t>
+          <t>9977.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>14172.4</t>
+          <t>13715.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>11559.0</t>
+          <t>11377.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>37408.86</t>
+          <t>36959.5</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3363.749922500897</t>
+          <t>-3055.506542605452</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-1267.1</v>
+        <v>-1360.17</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-16.01</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>150.97</t>
+          <t>149.19</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>34.27</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2443380.4</t>
+          <t>2382965.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1233866.56</t>
+          <t>1217959.22</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>326866.16</v>
+        <v>158481.26</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,42 +1455,42 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1995498.4</t>
+          <t>2443380.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1183171.94</t>
+          <t>1233866.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>223952.94</v>
+        <v>326866.16</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>210.228</t>
+          <t>42.716</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-68.41</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1971587.4</t>
+          <t>1995498.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1383171.1</t>
+          <t>1447308.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1209715.2</t>
+          <t>1183171.94</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>588416</t>
+          <t>548190</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>21396.27799944613</t>
+          <t>52558.84065871156</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>330373.73</v>
+        <v>223952.94</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>210.228</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.04</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1097188.6</t>
+          <t>1971587.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1002558.1</t>
+          <t>1383171.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1151381.24</t>
+          <t>1209715.2</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>94630</t>
+          <t>588416</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-34781.43987228681</t>
+          <t>21396.27799944613</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>21726.9</v>
+        <v>330373.73</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,42 +2602,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>68.61</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>28.002</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-2.87</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2733,72 +2733,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-26.97</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.07</t>
+          <t>-103.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>699699.0</t>
+          <t>1724881.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>902862.4</t>
+          <t>1097188.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>908805.3</t>
+          <t>1002558.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1262902.06</t>
+          <t>1151381.24</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5942</t>
+          <t>94630</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-45055.68381211576</t>
+          <t>-34781.43987228681</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-42950.34</v>
+        <v>21726.9</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>50.125</t>
+          <t>28.002</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3189,17 +3189,17 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-39.78</t>
+          <t>-26.97</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.87</t>
+          <t>-103.07</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1254915.0</t>
+          <t>699699.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>939932.6</t>
+          <t>902862.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>906688.0</t>
+          <t>908805.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1280505.3</t>
+          <t>1262902.06</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>-5942</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-45438.47287292028</t>
+          <t>-45055.68381211576</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-23971.54</v>
+        <v>-42950.34</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3464,34 +3464,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>50.125</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>37.399</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.67</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,32 +3595,32 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3645,22 +3645,22 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-58.11</t>
+          <t>-39.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-102.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>934682.0</t>
+          <t>1254915.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>899118.2</t>
+          <t>939932.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>945049.3</t>
+          <t>906688.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1319081.6</t>
+          <t>1280505.3</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-45931</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-49341.55158763187</t>
+          <t>-45438.47287292028</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-55490.26</v>
+        <v>-23971.54</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>34.748</t>
+          <t>37.399</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,79 +4026,79 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>25.03</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>25.17</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>25.28</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-58.11</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.04</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>25.19</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>25.29</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>24.93</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-69.68</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.21</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>871766.0</t>
+          <t>934682.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>794754.8</t>
+          <t>899118.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>979822.2</t>
+          <t>945049.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1367719.62</t>
+          <t>1319081.6</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>-45931</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-48223.60371391037</t>
+          <t>-49341.55158763187</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-64224.54</v>
+        <v>-55490.26</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>25.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>25.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>34.748</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-18.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,52 +4457,52 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-99.33</t>
+          <t>-69.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.82</t>
+          <t>-102.21</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>753250.0</t>
+          <t>871766.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>907927.6</t>
+          <t>794754.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1067569.3</t>
+          <t>979822.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1387727.28</t>
+          <t>1367719.62</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-159641</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-45314.34237515743</t>
+          <t>-48223.60371391037</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-67667.34</v>
+        <v>-64224.54</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,22 +4655,22 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>12.32</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35.302</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-12.94</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,67 +4888,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>25.29</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-178.18</t>
+          <t>-99.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.37</t>
+          <t>-101.82</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>885050.0</t>
+          <t>753250.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>914748.2</t>
+          <t>907927.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1050650.7</t>
+          <t>1067569.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1426103.62</t>
+          <t>1387727.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-135902</t>
+          <t>-159641</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-41250.1601028585</t>
+          <t>-45314.34237515743</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-57470.8</v>
+        <v>-67667.34</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,14 +5141,14 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
           <t>25.0</t>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>35.302</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-12.94</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5319,67 +5319,67 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-375.04</t>
+          <t>-178.18</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.76</t>
+          <t>-101.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11944425.59674923</t>
+          <t>11926886.20247295</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1050843.0</t>
+          <t>885050.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>873443.4</t>
+          <t>914748.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1049354.7</t>
+          <t>1050650.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1428606.16</t>
+          <t>1426103.62</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-175911</t>
+          <t>-135902</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-38300.95243717273</t>
+          <t>-41250.1601028585</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-54973.21</v>
+        <v>-57470.8</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5755,52 +5755,52 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.62</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>52.35</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>13502.2</t>
+          <t>14010.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>25275.3</t>
+          <t>24459.88</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-1059.74</v>
+        <v>-951.83</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-28.52</t>
+          <t>-27.01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,37 +6201,37 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.35</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>13402.8</t>
+          <t>13502.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>28099.9</t>
+          <t>25275.3</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-473.08</v>
+        <v>-1059.74</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-28.76</t>
+          <t>-28.52</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,37 +6632,37 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.04</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>52.81</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-29.28</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-124.89</t>
+          <t>-126.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>13127.2</t>
+          <t>13402.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>18427.5</t>
+          <t>18750.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31635.06</t>
+          <t>28099.9</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-5300</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-575.2561739766202</t>
+          <t>-559.5370652281069</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-377.96</v>
+        <v>-473.08</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-22.77</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-28.76</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.14</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,64 +7058,64 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.81</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>-0.79</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-124.89</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15436.0</t>
+          <t>13127.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>19028.5</t>
+          <t>18427.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>32867.0</t>
+          <t>31635.06</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-3592</t>
+          <t>-5300</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-611.1283719113699</t>
+          <t>-575.2561739766202</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-81.79000000000001</v>
+        <v>-377.96</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-21.12</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.03</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-16.14</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,17 +7489,17 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -7509,42 +7509,42 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>53.81</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11478.0</t>
+          <t>20848.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>19367.4</t>
+          <t>15436.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18899.4</t>
+          <t>19028.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>33340.5</t>
+          <t>32867.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-3592</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-707.3726211353406</t>
+          <t>-611.1283719113699</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-477.44</v>
+        <v>-81.79000000000001</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-21.12</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7910,52 +7910,52 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>53.34</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-124.61</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6960.0</t>
+          <t>11478.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23495.6</t>
+          <t>19367.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>18605.3</t>
+          <t>18899.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>34041.78</t>
+          <t>33340.5</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-749.1791258508009</t>
+          <t>-707.3726211353406</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-21.67</v>
+        <v>-477.44</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-17.00</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>259.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8341,52 +8341,52 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>63.34</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>51.42</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>53.34</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-124.61</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13171.0</t>
+          <t>6960.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>24099.0</t>
+          <t>23495.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>19135.7</t>
+          <t>18605.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>34590.34</t>
+          <t>34041.78</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-881.4528072961443</t>
+          <t>-749.1791258508009</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>1114.26</v>
+        <v>-21.67</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-17.16</t>
+          <t>-17.00</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>480.0</t>
+          <t>259.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-10.7</t>
+          <t>-6.7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8772,52 +8772,52 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -8827,17 +8827,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-129.04</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>24723.0</t>
+          <t>13171.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>23727.8</t>
+          <t>24099.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>18741.0</t>
+          <t>19135.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>35788.92</t>
+          <t>34590.34</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1244.309966990364</t>
+          <t>-881.4528072961443</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>2031.77</v>
+        <v>1114.26</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-17.16</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>754.0</t>
+          <t>480.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-8.82</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>26.61</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9203,72 +9203,72 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.46</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>93.06</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>51.64</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>50.54</t>
+          <t>50.48</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>53.78</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.81</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-129.04</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>40505.0</t>
+          <t>24723.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22621.0</t>
+          <t>23727.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>17398.2</t>
+          <t>18741.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>35945.06</t>
+          <t>35788.92</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1839.960353031046</t>
+          <t>-1244.309966990364</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>2032.21</v>
+        <v>2031.77</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>605.0</t>
+          <t>754.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-13.95</t>
+          <t>-12.01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>93.06</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>51.08</t>
+          <t>51.64</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>50.53</t>
+          <t>50.54</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>53.78</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>53.76</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-136.39</t>
+          <t>-132.48</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>32119.0</t>
+          <t>40505.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>18431.4</t>
+          <t>22621.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13998.9</t>
+          <t>17398.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>35870.44</t>
+          <t>35945.06</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-2543.991694015614</t>
+          <t>-1839.960353031046</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>269.34</v>
+        <v>2032.21</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>605.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-12.01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>51.08</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>50.53</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>53.99</t>
+          <t>53.88</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>53.74</t>
+          <t>53.76</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-139.68</t>
+          <t>-136.39</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>100113.196685879</t>
+          <t>99999.40359712232</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9977.0</t>
+          <t>32119.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>13715.0</t>
+          <t>18431.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>11377.1</t>
+          <t>13998.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>36959.5</t>
+          <t>35870.44</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3055.506542605452</t>
+          <t>-2543.991694015614</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-1360.17</v>
+        <v>269.34</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-16.01</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>149.19</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,42 +1014,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2330704.4</t>
+          <t>1437406.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1227934.96</t>
+          <t>1217210.96</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1463575</v>
+        <v>777270</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2382965.6</t>
+          <t>2330704.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1217959.22</t>
+          <t>1227934.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>397625</v>
+        <v>1463575</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2443380.4</t>
+          <t>2382965.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1233866.56</t>
+          <t>1217959.22</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>326866.1581960404</t>
+          <t>158481.2602790978</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>3494325</v>
+        <v>397625</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,42 +2337,42 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1995498.4</t>
+          <t>2443380.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1183171.94</t>
+          <t>1233866.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>223952.9352846714</t>
+          <t>326866.1581960404</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1054237</v>
+        <v>3494325</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>210.228</t>
+          <t>42.716</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,42 +2773,42 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-68.41</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1971587.4</t>
+          <t>1995498.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1383171.1</t>
+          <t>1447308.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1209715.2</t>
+          <t>1183171.94</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>588416</t>
+          <t>548190</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>21396.27799944613</t>
+          <t>52558.84065871156</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>330373.7262939773</t>
+          <t>223952.9352846714</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>5243760</v>
+        <v>1054237</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>210.228</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.04</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1097188.6</t>
+          <t>1971587.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1002558.1</t>
+          <t>1383171.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1151381.24</t>
+          <t>1209715.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>94630</t>
+          <t>588416</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-34781.43987228681</t>
+          <t>21396.27799944613</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>21726.90179677238</t>
+          <t>330373.7262939773</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1724881</v>
+        <v>5243760</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,42 +3499,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>68.61</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>28.002</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3630,72 +3630,72 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-26.97</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.07</t>
+          <t>-103.04</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>699699.0</t>
+          <t>1724881.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>902862.4</t>
+          <t>1097188.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>908805.3</t>
+          <t>1002558.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1262902.06</t>
+          <t>1151381.24</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5942</t>
+          <t>94630</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-45055.68381211576</t>
+          <t>-34781.43987228681</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-42950.34397769091</t>
+          <t>21726.90179677238</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>699699</v>
+        <v>1724881</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50.125</t>
+          <t>28.002</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-39.78</t>
+          <t>-26.97</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.87</t>
+          <t>-103.07</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1254915.0</t>
+          <t>699699.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>939932.6</t>
+          <t>902862.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>906688.0</t>
+          <t>908805.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1280505.3</t>
+          <t>1262902.06</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>-5942</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-45438.47287292028</t>
+          <t>-45055.68381211576</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-23971.53994200658</t>
+          <t>-42950.34397769091</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1254915</v>
+        <v>699699</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>37.399</t>
+          <t>50.125</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,32 +4502,32 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4552,22 +4552,22 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-58.11</t>
+          <t>-39.78</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-102.87</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>934682.0</t>
+          <t>1254915.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>899118.2</t>
+          <t>939932.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>945049.3</t>
+          <t>906688.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1319081.6</t>
+          <t>1280505.3</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-45931</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-49341.55158763187</t>
+          <t>-45438.47287292028</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-55490.26489310013</t>
+          <t>-23971.53994200658</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>934682</v>
+        <v>1254915</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>34.748</t>
+          <t>37.399</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,79 +4938,79 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>25.03</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>25.17</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>25.28</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-58.11</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.04</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>25.19</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>25.29</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>24.93</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-69.68</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.21</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>871766.0</t>
+          <t>934682.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>794754.8</t>
+          <t>899118.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>979822.2</t>
+          <t>945049.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1367719.62</t>
+          <t>1319081.6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>-45931</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-48223.60371391037</t>
+          <t>-49341.55158763187</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-64224.54107705154</t>
+          <t>-55490.26489310013</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>871766</v>
+        <v>934682</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>25.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>25.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>34.748</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-18.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,52 +5374,52 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.19</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-99.33</t>
+          <t>-69.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.82</t>
+          <t>-102.21</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11911868.41898148</t>
+          <t>11895310.69414484</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>753250.0</t>
+          <t>871766.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>907927.6</t>
+          <t>794754.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1067569.3</t>
+          <t>979822.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1387727.28</t>
+          <t>1367719.62</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-159641</t>
+          <t>-185067</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-45314.34237515743</t>
+          <t>-48223.60371391037</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-67667.34487280156</t>
+          <t>-64224.54107705154</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>753250</v>
+        <v>871766</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,22 +5577,22 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.16</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>49.36</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>51.92</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-29.79</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>12677.4</t>
+          <t>11302.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>24098.68</t>
+          <t>23633.42</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>14184</v>
+        <v>6302</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>49.62</t>
+          <t>49.36</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>51.92</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>14010.2</t>
+          <t>12677.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>24459.88</t>
+          <t>24098.68</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>14018</v>
+        <v>14184</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,57 +6682,57 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.62</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>52.35</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>13502.2</t>
+          <t>14010.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>25275.3</t>
+          <t>24459.88</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1059.740935176555</t>
+          <t>-951.8336894428303</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>7457</v>
+        <v>14018</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-28.52</t>
+          <t>-27.01</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,37 +7138,37 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.35</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7178,17 +7178,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>13402.8</t>
+          <t>13502.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>28099.9</t>
+          <t>25275.3</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-473.081967111284</t>
+          <t>-1059.740935176555</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>14549</v>
+        <v>7457</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-28.76</t>
+          <t>-28.52</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,37 +7574,37 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.04</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>52.81</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -7614,17 +7614,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-29.28</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-124.89</t>
+          <t>-126.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>13127.2</t>
+          <t>13402.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18427.5</t>
+          <t>18750.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>31635.06</t>
+          <t>28099.9</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-5300</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-575.2561739766202</t>
+          <t>-559.5370652281069</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-377.9590853354966</t>
+          <t>-473.081967111284</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>13179</v>
+        <v>14549</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-22.77</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-28.76</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.14</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,64 +8005,64 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.81</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>-0.79</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-124.89</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>15436.0</t>
+          <t>13127.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>19028.5</t>
+          <t>18427.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>32867.0</t>
+          <t>31635.06</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-3592</t>
+          <t>-5300</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-611.1283719113699</t>
+          <t>-575.2561739766202</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-81.78500117953081</t>
+          <t>-377.9590853354966</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>20848</v>
+        <v>13179</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-21.12</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-16.14</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -8461,42 +8461,42 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>53.81</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11478.0</t>
+          <t>20848.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19367.4</t>
+          <t>15436.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18899.4</t>
+          <t>19028.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>33340.5</t>
+          <t>32867.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-3592</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-707.3726211353406</t>
+          <t>-611.1283719113699</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-477.4368452003091</t>
+          <t>-81.78500117953081</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>11478</v>
+        <v>20848</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-21.12</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,57 +8862,57 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>53.34</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -8922,17 +8922,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-124.61</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6960.0</t>
+          <t>11478.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>23495.6</t>
+          <t>19367.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>18605.3</t>
+          <t>18899.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>34041.78</t>
+          <t>33340.5</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-749.1791258508009</t>
+          <t>-707.3726211353406</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-21.6738779014122</t>
+          <t>-477.4368452003091</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>6960</v>
+        <v>11478</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-17.00</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>259.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,57 +9298,57 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>63.34</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>51.42</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>53.34</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-124.61</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>13171.0</t>
+          <t>6960.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>24099.0</t>
+          <t>23495.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>19135.7</t>
+          <t>18605.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>34590.34</t>
+          <t>34041.78</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-881.4528072961443</t>
+          <t>-749.1791258508009</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1114.261571022063</t>
+          <t>-21.6738779014122</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>13171</v>
+        <v>6960</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-17.16</t>
+          <t>-17.00</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>480.0</t>
+          <t>259.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,102 +9628,102 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>25.94</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-05-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-05-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>54.8</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>54.8</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-11.93</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>6.57</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
           <t>-3.78</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>26.61</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-05-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-05-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>54.8</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>54.8</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-10.18</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>6.57</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>4.16</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>-3.09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,57 +9734,57 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -9794,17 +9794,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-129.04</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>24723.0</t>
+          <t>13171.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>23727.8</t>
+          <t>24099.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18741.0</t>
+          <t>19135.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>35788.92</t>
+          <t>34590.34</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1244.309966990364</t>
+          <t>-881.4528072961443</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2031.767156233385</t>
+          <t>1114.261571022063</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>24723</v>
+        <v>13171</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-17.16</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>754.0</t>
+          <t>480.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-11.3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>26.61</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.46</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>93.06</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>51.64</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>50.54</t>
+          <t>50.48</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>53.78</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.81</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-132.48</t>
+          <t>-129.04</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>99886.2952586207</t>
+          <t>99756.54878048782</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>40505.0</t>
+          <t>24723.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>22621.0</t>
+          <t>23727.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>17398.2</t>
+          <t>18741.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>35945.06</t>
+          <t>35788.92</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1839.960353031046</t>
+          <t>-1244.309966990364</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2032.212022384079</t>
+          <t>2031.767156233385</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>40505</v>
+        <v>24723</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-13.04</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>145.16</t>
+          <t>148.39</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31.352</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>-19.00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,52 +1014,52 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1437406.4</t>
+          <t>1358383.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1217210.96</t>
+          <t>1212587.6</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>777270</v>
+        <v>659122</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,42 +1450,42 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2330704.4</t>
+          <t>1437406.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1227934.96</t>
+          <t>1217210.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1463575</v>
+        <v>777270</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2382965.6</t>
+          <t>2330704.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1217959.22</t>
+          <t>1227934.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>397625</v>
+        <v>1463575</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2443380.4</t>
+          <t>2382965.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1233866.56</t>
+          <t>1217959.22</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>326866.1581960404</t>
+          <t>158481.2602790978</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>3494325</v>
+        <v>397625</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,42 +2773,42 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1995498.4</t>
+          <t>2443380.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1183171.94</t>
+          <t>1233866.56</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>223952.9352846714</t>
+          <t>326866.1581960404</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1054237</v>
+        <v>3494325</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>210.228</t>
+          <t>42.716</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,42 +3209,42 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-68.41</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1971587.4</t>
+          <t>1995498.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1383171.1</t>
+          <t>1447308.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1209715.2</t>
+          <t>1183171.94</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>588416</t>
+          <t>548190</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>21396.27799944613</t>
+          <t>52558.84065871156</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>330373.7262939773</t>
+          <t>223952.9352846714</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>5243760</v>
+        <v>1054237</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>210.228</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.04</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1097188.6</t>
+          <t>1971587.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1002558.1</t>
+          <t>1383171.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1151381.24</t>
+          <t>1209715.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>94630</t>
+          <t>588416</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-34781.43987228681</t>
+          <t>21396.27799944613</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>21726.90179677238</t>
+          <t>330373.7262939773</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1724881</v>
+        <v>5243760</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,34 +3935,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>68.61</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>28.002</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4066,72 +4066,72 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-26.97</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.07</t>
+          <t>-103.04</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>699699.0</t>
+          <t>1724881.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>902862.4</t>
+          <t>1097188.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>908805.3</t>
+          <t>1002558.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1262902.06</t>
+          <t>1151381.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5942</t>
+          <t>94630</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-45055.68381211576</t>
+          <t>-34781.43987228681</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-42950.34397769091</t>
+          <t>21726.90179677238</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>699699</v>
+        <v>1724881</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>50.125</t>
+          <t>28.002</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4527,17 +4527,17 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-39.78</t>
+          <t>-26.97</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.87</t>
+          <t>-103.07</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1254915.0</t>
+          <t>699699.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>939932.6</t>
+          <t>902862.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>906688.0</t>
+          <t>908805.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1280505.3</t>
+          <t>1262902.06</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>-5942</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-45438.47287292028</t>
+          <t>-45055.68381211576</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-23971.53994200658</t>
+          <t>-42950.34397769091</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1254915</v>
+        <v>699699</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>37.399</t>
+          <t>50.125</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,32 +4938,32 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-58.11</t>
+          <t>-39.78</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-102.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>934682.0</t>
+          <t>1254915.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>899118.2</t>
+          <t>939932.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>945049.3</t>
+          <t>906688.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1319081.6</t>
+          <t>1280505.3</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-45931</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-49341.55158763187</t>
+          <t>-45438.47287292028</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-55490.26489310013</t>
+          <t>-23971.53994200658</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>934682</v>
+        <v>1254915</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>34.748</t>
+          <t>37.399</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-18.89</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,79 +5374,79 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>25.03</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>25.17</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>25.28</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-58.11</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.04</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>25.19</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>25.29</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>24.93</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-69.68</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.21</t>
+          <t>-102.58</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11895310.69414484</t>
+          <t>11878531.26692308</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>871766.0</t>
+          <t>934682.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>794754.8</t>
+          <t>899118.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>979822.2</t>
+          <t>945049.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1367719.62</t>
+          <t>1319081.6</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-185067</t>
+          <t>-45931</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-48223.60371391037</t>
+          <t>-49341.55158763187</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-64224.54107705154</t>
+          <t>-55490.26489310013</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>871766</v>
+        <v>934682</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>25.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>25.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.02999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-29.79</t>
+          <t>-24.50</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-137.83</t>
+          <t>-140.30</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -5915,31 +5915,31 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>12214.6</t>
+          <t>12352.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23633.42</t>
+          <t>23372.88</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-1050</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-804.7199680471464</t>
+          <t>-838.5264920236409</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1331.954815838546</t>
+          <t>-1024.462373894361</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>6302</v>
+        <v>14549</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>49.36</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>51.92</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-29.79</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12677.4</t>
+          <t>11302.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>24098.68</t>
+          <t>23633.42</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>14184</v>
+        <v>6302</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>49.62</t>
+          <t>49.36</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>51.92</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>14010.2</t>
+          <t>12677.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>24459.88</t>
+          <t>24098.68</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>14018</v>
+        <v>14184</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,57 +7118,57 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.62</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>52.35</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7178,17 +7178,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>13502.2</t>
+          <t>14010.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>25275.3</t>
+          <t>24459.88</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1059.740935176555</t>
+          <t>-951.8336894428303</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>7457</v>
+        <v>14018</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-28.52</t>
+          <t>-27.01</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,37 +7574,37 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.35</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -7614,17 +7614,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>13402.8</t>
+          <t>13502.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28099.9</t>
+          <t>25275.3</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-473.081967111284</t>
+          <t>-1059.740935176555</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>14549</v>
+        <v>7457</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-28.76</t>
+          <t>-28.52</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,37 +8010,37 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.04</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>52.81</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8050,17 +8050,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-29.28</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-124.89</t>
+          <t>-126.86</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>13127.2</t>
+          <t>13402.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>18427.5</t>
+          <t>18750.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>31635.06</t>
+          <t>28099.9</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-5300</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-575.2561739766202</t>
+          <t>-559.5370652281069</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-377.9590853354966</t>
+          <t>-473.081967111284</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>13179</v>
+        <v>14549</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-22.77</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-28.76</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.14</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,64 +8441,64 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.81</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
           <t>-0.79</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-124.89</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>15436.0</t>
+          <t>13127.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>19028.5</t>
+          <t>18427.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>32867.0</t>
+          <t>31635.06</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-3592</t>
+          <t>-5300</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-611.1283719113699</t>
+          <t>-575.2561739766202</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-81.78500117953081</t>
+          <t>-377.9590853354966</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>20848</v>
+        <v>13179</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-21.12</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-16.14</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,17 +8877,17 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -8897,42 +8897,42 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>53.81</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>11478.0</t>
+          <t>20848.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>19367.4</t>
+          <t>15436.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>18899.4</t>
+          <t>19028.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>33340.5</t>
+          <t>32867.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-3592</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-707.3726211353406</t>
+          <t>-611.1283719113699</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-477.4368452003091</t>
+          <t>-81.78500117953081</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>11478</v>
+        <v>20848</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-21.12</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,57 +9298,57 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>53.34</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-124.61</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>6960.0</t>
+          <t>11478.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>23495.6</t>
+          <t>19367.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>18605.3</t>
+          <t>18899.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>34041.78</t>
+          <t>33340.5</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-749.1791258508009</t>
+          <t>-707.3726211353406</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-21.6738779014122</t>
+          <t>-477.4368452003091</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>6960</v>
+        <v>11478</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-17.00</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>259.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-9.71</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,57 +9734,57 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>63.34</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>51.42</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>53.34</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -9794,17 +9794,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-124.61</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>13171.0</t>
+          <t>6960.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>24099.0</t>
+          <t>23495.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>19135.7</t>
+          <t>18605.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>34590.34</t>
+          <t>34041.78</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-881.4528072961443</t>
+          <t>-749.1791258508009</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1114.261571022063</t>
+          <t>-21.6738779014122</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>13171</v>
+        <v>6960</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-17.16</t>
+          <t>-17.00</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>480.0</t>
+          <t>259.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-11.3</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,57 +10170,57 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.54</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -10230,17 +10230,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-129.04</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>99756.54878048782</t>
+          <t>99644.89684813755</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>24723.0</t>
+          <t>13171.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>23727.8</t>
+          <t>24099.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>18741.0</t>
+          <t>19135.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>35788.92</t>
+          <t>34590.34</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1244.309966990364</t>
+          <t>-881.4528072961443</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2031.767156233385</t>
+          <t>1114.261571022063</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>24723</v>
+        <v>13171</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-17.16</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>148.39</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-52.42</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,47 +1014,47 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1069,24 +1069,24 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.09</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1358383.4</t>
+          <t>762768.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1676940.9</t>
+          <t>1603074.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1212587.6</t>
+          <t>1210877.9</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-318557</t>
+          <t>-840306</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>75026.98496404906</t>
+          <t>49174.2840013071</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-35389.88503614976</t>
+          <t>-93015.5712937736</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>659122</v>
+        <v>516249</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31.352</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>-19.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,52 +1450,52 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1505,17 +1505,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1437406.4</t>
+          <t>1358383.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1217210.96</t>
+          <t>1212587.6</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>777270</v>
+        <v>659122</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,102 +1780,102 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-15.67</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>35.98</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-1.97</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,42 +1886,42 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2330704.4</t>
+          <t>1437406.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1227934.96</t>
+          <t>1217210.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1463575</v>
+        <v>777270</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2382965.6</t>
+          <t>2330704.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1217959.22</t>
+          <t>1227934.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>397625</v>
+        <v>1463575</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2443380.4</t>
+          <t>2382965.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1233866.56</t>
+          <t>1217959.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>326866.1581960404</t>
+          <t>158481.2602790978</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>3494325</v>
+        <v>397625</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,42 +3209,42 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1995498.4</t>
+          <t>2443380.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1183171.94</t>
+          <t>1233866.56</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>223952.9352846714</t>
+          <t>326866.1581960404</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1054237</v>
+        <v>3494325</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>210.228</t>
+          <t>42.716</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,42 +3645,42 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-68.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1971587.4</t>
+          <t>1995498.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1383171.1</t>
+          <t>1447308.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1209715.2</t>
+          <t>1183171.94</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>588416</t>
+          <t>548190</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>21396.27799944613</t>
+          <t>52558.84065871156</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>330373.7262939773</t>
+          <t>223952.9352846714</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>5243760</v>
+        <v>1054237</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>210.228</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.04</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1097188.6</t>
+          <t>1971587.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1002558.1</t>
+          <t>1383171.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1151381.24</t>
+          <t>1209715.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>94630</t>
+          <t>588416</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-34781.43987228681</t>
+          <t>21396.27799944613</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>21726.90179677238</t>
+          <t>330373.7262939773</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1724881</v>
+        <v>5243760</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,42 +4371,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>68.61</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>28.002</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4502,72 +4502,72 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-26.97</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.07</t>
+          <t>-103.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>699699.0</t>
+          <t>1724881.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>902862.4</t>
+          <t>1097188.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>908805.3</t>
+          <t>1002558.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1262902.06</t>
+          <t>1151381.24</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5942</t>
+          <t>94630</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-45055.68381211576</t>
+          <t>-34781.43987228681</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-42950.34397769091</t>
+          <t>21726.90179677238</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>699699</v>
+        <v>1724881</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>50.125</t>
+          <t>28.002</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4963,17 +4963,17 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-39.78</t>
+          <t>-26.97</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.87</t>
+          <t>-103.07</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1254915.0</t>
+          <t>699699.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>939932.6</t>
+          <t>902862.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>906688.0</t>
+          <t>908805.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1280505.3</t>
+          <t>1262902.06</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>-5942</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-45438.47287292028</t>
+          <t>-45055.68381211576</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-23971.53994200658</t>
+          <t>-42950.34397769091</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1254915</v>
+        <v>699699</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>37.399</t>
+          <t>50.125</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,32 +5374,32 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -5424,22 +5424,22 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-58.11</t>
+          <t>-39.78</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.58</t>
+          <t>-102.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11878531.26692308</t>
+          <t>11861474.18894009</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>934682.0</t>
+          <t>1254915.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>899118.2</t>
+          <t>939932.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>945049.3</t>
+          <t>906688.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1319081.6</t>
+          <t>1280505.3</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-45931</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-49341.55158763187</t>
+          <t>-45438.47287292028</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-55490.26489310013</t>
+          <t>-23971.53994200658</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>934682</v>
+        <v>1254915</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8.50</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,72 +5815,72 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.02999999999999</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.87</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>51.33</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-24.50</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-140.30</t>
+          <t>-141.95</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>11302.0</t>
+          <t>12674.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>12352.4</t>
+          <t>13088.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23372.88</t>
+          <t>21902.1</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1050</t>
+          <t>-413</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-838.5264920236409</t>
+          <t>-832.7079709717071</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1024.462373894361</t>
+          <t>-800.706105186071</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>14549</v>
+        <v>14321</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,72 +6251,72 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.02999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-29.79</t>
+          <t>-24.50</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-137.83</t>
+          <t>-140.30</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -6351,31 +6351,31 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>12214.6</t>
+          <t>12352.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>23633.42</t>
+          <t>23372.88</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-1050</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-804.7199680471464</t>
+          <t>-838.5264920236409</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1331.954815838546</t>
+          <t>-1024.462373894361</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>6302</v>
+        <v>14549</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,72 +6687,72 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>49.36</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>51.92</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-29.79</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>12677.4</t>
+          <t>11302.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>24098.68</t>
+          <t>23633.42</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>14184</v>
+        <v>6302</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>49.62</t>
+          <t>49.36</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>51.92</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>14010.2</t>
+          <t>12677.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24459.88</t>
+          <t>24098.68</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>14018</v>
+        <v>14184</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,52 +7559,52 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.62</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>52.35</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -7614,17 +7614,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>13502.2</t>
+          <t>14010.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>25275.3</t>
+          <t>24459.88</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1059.740935176555</t>
+          <t>-951.8336894428303</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>7457</v>
+        <v>14018</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-28.52</t>
+          <t>-27.01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,37 +8010,37 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.35</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8050,17 +8050,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>13402.8</t>
+          <t>13502.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28099.9</t>
+          <t>25275.3</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-473.081967111284</t>
+          <t>-1059.740935176555</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>14549</v>
+        <v>7457</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-28.76</t>
+          <t>-28.52</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,37 +8446,37 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.04</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>52.81</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8486,17 +8486,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-29.28</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-124.89</t>
+          <t>-126.86</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>13127.2</t>
+          <t>13402.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18427.5</t>
+          <t>18750.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>31635.06</t>
+          <t>28099.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-5300</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-575.2561739766202</t>
+          <t>-559.5370652281069</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-377.9590853354966</t>
+          <t>-473.081967111284</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>13179</v>
+        <v>14549</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-22.77</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-28.76</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-16.14</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,64 +8877,64 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.81</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>-0.79</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-124.89</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>15436.0</t>
+          <t>13127.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>19028.5</t>
+          <t>18427.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>32867.0</t>
+          <t>31635.06</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-3592</t>
+          <t>-5300</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-611.1283719113699</t>
+          <t>-575.2561739766202</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-81.78500117953081</t>
+          <t>-377.9590853354966</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>20848</v>
+        <v>13179</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-21.12</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-16.14</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,17 +9313,17 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -9333,42 +9333,42 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>53.81</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>11478.0</t>
+          <t>20848.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>19367.4</t>
+          <t>15436.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>18899.4</t>
+          <t>19028.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>33340.5</t>
+          <t>32867.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-3592</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-707.3726211353406</t>
+          <t>-611.1283719113699</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-477.4368452003091</t>
+          <t>-81.78500117953081</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>11478</v>
+        <v>20848</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-21.12</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,52 +9739,52 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>50.49</t>
+          <t>50.44</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>53.34</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -9794,17 +9794,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-124.61</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6960.0</t>
+          <t>11478.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>23495.6</t>
+          <t>19367.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18605.3</t>
+          <t>18899.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>34041.78</t>
+          <t>33340.5</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-749.1791258508009</t>
+          <t>-707.3726211353406</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-21.6738779014122</t>
+          <t>-477.4368452003091</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>6960</v>
+        <v>11478</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-17.00</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>259.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.75</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,52 +10175,52 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>63.34</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>51.42</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.49</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>53.34</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -10230,17 +10230,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-124.61</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>99644.89684813755</t>
+          <t>99533.07510729613</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>13171.0</t>
+          <t>6960.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>24099.0</t>
+          <t>23495.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>19135.7</t>
+          <t>18605.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>34590.34</t>
+          <t>34041.78</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-881.4528072961443</t>
+          <t>-749.1791258508009</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1114.261571022063</t>
+          <t>-21.6738779014122</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>13171</v>
+        <v>6960</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-17.16</t>
+          <t>-17.00</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>150.32</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>24.98</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>24.97</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>25.15</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>516249.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>762768.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>762768.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1603074.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1210877.9</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1210877.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-93015.5712937736</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>516249</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>516249.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>24.84</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>24.97</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>25.15</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>659122.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1358383.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1358383.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1676940.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1212587.6</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1212587.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-35389.88503614976</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>659122</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>659122.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>24.72</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>24.96</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>25.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>777270.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1437406.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1437406.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1704496.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1217210.96</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1217210.96</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>32888.62694031815</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>777270</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>777270.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>24.72</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>24.98</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>25.16</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>25.16</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1463575.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2330704.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2330704.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1713946.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1227934.96</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1227934.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>116596.0502302607</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1463575</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1463575.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>24.79</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>25.17</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>397625.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2382965.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2382965.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1642914.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1217959.22</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1217959.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>158481.2602790978</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>397625</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>397625.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>24.8</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>25.03</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>25.18</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>25.18</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3494325.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2443380.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2443380.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1691656.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1233866.56</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1233866.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>326866.1581960404</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3494325</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3494325.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>24.94</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>25.08</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>25.2</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1054237.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1995498.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1995498.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1447308.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1183171.94</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1183171.94</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>223952.9352846714</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1054237</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1054237.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>25.02</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>25.12</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>5243760.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1971587.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1971587.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1383171.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1209715.2</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1209715.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>330373.7262939773</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>5243760</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5243760.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>25.07</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>25.14</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>25.24</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>25.24</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1724881.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1097188.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1097188.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1002558.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1151381.24</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1151381.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>21726.90179677238</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1724881</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1724881.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>25.05</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>25.16</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>25.26</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>25.26</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>699699.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>902862.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>902862.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>908805.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1262902.06</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1262902.06</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-42950.34397769091</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>699699</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>699699.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>25.05</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>25.27</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>25.27</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1254915.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>939932.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>939932.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>906688.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1280505.3</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1280505.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-23971.53994200658</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1254915</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1254915.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>46.1</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>48.87</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>51.33</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>51.33</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>14321.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>12674.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>12674.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>13088.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>21902.1</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>21902.1</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-800.706105186071</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>14321</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>14321.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>46.02999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>48.99</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>51.52</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>51.52</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>14549.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>11302.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>11302</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>12352.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>23372.88</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>23372.88</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1024.462373894361</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>14549</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>14549.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>46.22</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>51.72</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>49.16</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>51.72</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>6302.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>11302.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>11302</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>12214.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>23633.42</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>23633.42</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-1331.954815838546</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>6302</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>6302.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>46.56</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>49.36</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>51.92</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>51.92</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>14184.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>12677.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>12677.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>14056.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>24098.68</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>24098.68</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-840.0527751931495</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>14184</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>14184.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>47.12</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>49.62</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>52.16</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>52.16</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>14018.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>14010.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>14010.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>16688.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>24459.88</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>24459.88</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-951.8336894428303</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>14018</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>14018.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>47.61</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>49.81</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>52.35</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>52.35</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>7457.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>13502.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>13502.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>18498.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>25275.3</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>25275.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-1059.740935176555</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>7457</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>7457.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>48.42</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>50.04</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>52.56</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>52.56</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>14549.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>13402.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>13402.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>18750.9</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>28099.9</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>28099.9</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-473.081967111284</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>14549</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>14549.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>49.1</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>50.18</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>52.81</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>52.81</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>13179.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>13127.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>13127.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>18427.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>31635.06</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>31635.06</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-377.9590853354966</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>13179</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>13179.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>49.8</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>53</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>20848.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>15436.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>15436</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>19028.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>32867.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>32867</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-81.78500117953081</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>20848</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>20848.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>50.78</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>50.44</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>53.16</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>53.16</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>11478.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>19367.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>19367.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>18899.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>33340.5</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>33340.5</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-477.4368452003091</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>11478</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>11478.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>51.42</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>50.49</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>53.34</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>53.34</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>6960.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>23495.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>23495.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>18605.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>34041.78</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>34041.78</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-21.6738779014122</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>6960</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>6960.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>32.268</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-52.42</t>
+          <t>-47.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>94.12</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN2" t="n">
         <v>25.15</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.09</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>762768.2</v>
+        <v>845395.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1603074.3</t>
+          <t>1614180.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1210877.9</v>
+        <v>1212910.14</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-840306</t>
+          <t>-768785</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>49174.2840013071</t>
+          <t>24849.04609468049</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-93015.5712937736</t>
+          <t>-108939.7623917658</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-52.42</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,47 +1444,47 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -1495,24 +1495,24 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.09</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1358383.4</v>
+        <v>762768.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1676940.9</t>
+          <t>1603074.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1212587.6</v>
+        <v>1210877.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-318557</t>
+          <t>-840306</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>75026.98496404906</t>
+          <t>49174.2840013071</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-35389.88503614976</t>
+          <t>-93015.5712937736</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,34 +1743,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>31.352</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>-19.00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,68 +1874,68 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>24.96</v>
+        <v>24.97</v>
       </c>
       <c r="AN4" t="n">
         <v>25.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1437406.4</v>
+        <v>1358383.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1217210.96</v>
+        <v>1212587.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,42 +2304,42 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.98</v>
+        <v>24.96</v>
       </c>
       <c r="AN5" t="n">
-        <v>25.16</v>
+        <v>25.15</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2330704.4</v>
+        <v>1437406.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1227934.96</v>
+        <v>1217210.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>25</v>
+        <v>24.98</v>
       </c>
       <c r="AN6" t="n">
-        <v>25.17</v>
+        <v>25.16</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2382965.6</v>
+        <v>2330704.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1217959.22</v>
+        <v>1227934.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>25.03</v>
+        <v>25</v>
       </c>
       <c r="AN7" t="n">
-        <v>25.18</v>
+        <v>25.17</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2443380.4</v>
+        <v>2382965.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1233866.56</v>
+        <v>1217959.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>326866.1581960404</t>
+          <t>158481.2602790978</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,39 +3609,39 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>25.08</v>
+        <v>25.03</v>
       </c>
       <c r="AN8" t="n">
-        <v>25.2</v>
+        <v>25.18</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1995498.4</v>
+        <v>2443380.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1183171.94</v>
+        <v>1233866.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>223952.9352846714</t>
+          <t>326866.1581960404</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>210.228</t>
+          <t>42.716</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,39 +4039,39 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>25.12</v>
+        <v>25.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>25.22</v>
+        <v>25.2</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-68.41</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1971587.4</v>
+        <v>1995498.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1383171.1</t>
+          <t>1447308.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1209715.2</v>
+        <v>1183171.94</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>588416</t>
+          <t>548190</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21396.27799944613</t>
+          <t>52558.84065871156</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>330373.7262939773</t>
+          <t>223952.9352846714</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>210.228</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>25.14</v>
+        <v>25.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.24</v>
+        <v>25.22</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.04</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1097188.6</v>
+        <v>1971587.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1002558.1</t>
+          <t>1383171.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1151381.24</v>
+        <v>1209715.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>94630</t>
+          <t>588416</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-34781.43987228681</t>
+          <t>21396.27799944613</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>21726.90179677238</t>
+          <t>330373.7262939773</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,42 +4753,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>68.61</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>28.002</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4884,68 +4884,68 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>25.16</v>
+        <v>25.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.26</v>
+        <v>25.24</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-26.97</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.07</t>
+          <t>-103.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>699699.0</t>
+          <t>1724881.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>902862.4</v>
+        <v>1097188.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>908805.3</t>
+          <t>1002558.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1262902.06</v>
+        <v>1151381.24</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5942</t>
+          <t>94630</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-45055.68381211576</t>
+          <t>-34781.43987228681</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-42950.34397769091</t>
+          <t>21726.90179677238</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>699699.0</t>
+          <t>1724881.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50.125</t>
+          <t>28.002</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5358,10 +5358,10 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>25.17</v>
+        <v>25.16</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.27</v>
+        <v>25.26</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-39.78</t>
+          <t>-26.97</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.87</t>
+          <t>-103.07</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11861474.18894009</t>
+          <t>11845146.99156442</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1254915.0</t>
+          <t>699699.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>939932.6</v>
+        <v>902862.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>906688.0</t>
+          <t>908805.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1280505.3</v>
+        <v>1262902.06</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>-5942</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-45438.47287292028</t>
+          <t>-45055.68381211576</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-23971.53994200658</t>
+          <t>-42950.34397769091</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1254915.0</t>
+          <t>699699.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>53.74</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>48.87</v>
+        <v>48.78</v>
       </c>
       <c r="AN13" t="n">
-        <v>51.33</v>
+        <v>51.13</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-141.95</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>12674.8</v>
+        <v>12107.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>13088.5</t>
+          <t>13058.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>21902.1</v>
+        <v>18823.32</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-413</t>
+          <t>-951</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-832.7079709717071</t>
+          <t>-836.8273699700007</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-800.706105186071</t>
+          <t>-859.4840644606156</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-21.95</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-8.50</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.02999999999999</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>48.99</v>
+        <v>48.87</v>
       </c>
       <c r="AN14" t="n">
-        <v>51.52</v>
+        <v>51.33</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-24.50</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-140.30</t>
+          <t>-141.95</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>11302</v>
+        <v>12674.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>12352.4</t>
+          <t>13088.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>23372.88</v>
+        <v>21902.1</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1050</t>
+          <t>-413</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-838.5264920236409</t>
+          <t>-832.7079709717071</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1024.462373894361</t>
+          <t>-800.706105186071</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.02999999999999</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>49.16</v>
+        <v>48.99</v>
       </c>
       <c r="AN15" t="n">
-        <v>51.72</v>
+        <v>51.52</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-29.79</t>
+          <t>-24.50</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-137.83</t>
+          <t>-140.30</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
@@ -6703,30 +6703,30 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>12214.6</t>
+          <t>12352.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>23633.42</v>
+        <v>23372.88</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-1050</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-804.7199680471464</t>
+          <t>-838.5264920236409</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1331.954815838546</t>
+          <t>-1024.462373894361</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>49.36</v>
+        <v>49.16</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.92</v>
+        <v>51.72</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-29.79</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>12677.4</v>
+        <v>11302</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>24098.68</v>
+        <v>23633.42</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>49.62</v>
+        <v>49.36</v>
       </c>
       <c r="AN17" t="n">
-        <v>52.16</v>
+        <v>51.92</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>14010.2</v>
+        <v>12677.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>24459.88</v>
+        <v>24098.68</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,54 +7894,54 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>49.81</v>
+        <v>49.62</v>
       </c>
       <c r="AN18" t="n">
-        <v>52.35</v>
+        <v>52.16</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>13502.2</v>
+        <v>14010.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>25275.3</v>
+        <v>24459.88</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1059.740935176555</t>
+          <t>-951.8336894428303</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-28.52</t>
+          <t>-27.01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,34 +8344,34 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>50.04</v>
+        <v>49.81</v>
       </c>
       <c r="AN19" t="n">
-        <v>52.56</v>
+        <v>52.35</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>13402.8</v>
+        <v>13502.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>28099.9</v>
+        <v>25275.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-473.081967111284</t>
+          <t>-1059.740935176555</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-28.76</t>
+          <t>-28.52</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,34 +8774,34 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>50.18</v>
+        <v>50.04</v>
       </c>
       <c r="AN20" t="n">
-        <v>52.81</v>
+        <v>52.56</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-29.28</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-124.89</t>
+          <t>-126.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>13127.2</v>
+        <v>13402.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>18427.5</t>
+          <t>18750.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>31635.06</v>
+        <v>28099.9</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-5300</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-575.2561739766202</t>
+          <t>-559.5370652281069</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-377.9590853354966</t>
+          <t>-473.081967111284</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-22.77</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-28.76</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.14</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,60 +9199,60 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>50.3</v>
+        <v>50.18</v>
       </c>
       <c r="AN21" t="n">
-        <v>53</v>
+        <v>52.81</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>-0.79</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-124.89</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>15436</v>
+        <v>13127.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>19028.5</t>
+          <t>18427.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>32867</v>
+        <v>31635.06</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-3592</t>
+          <t>-5300</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-611.1283719113699</t>
+          <t>-575.2561739766202</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-81.78500117953081</t>
+          <t>-377.9590853354966</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-21.12</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-16.14</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -9649,38 +9649,38 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.44</v>
+        <v>50.3</v>
       </c>
       <c r="AN22" t="n">
-        <v>53.16</v>
+        <v>53</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>53.81</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>11478.0</t>
+          <t>20848.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>19367.4</v>
+        <v>15436</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18899.4</t>
+          <t>19028.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>33340.5</v>
+        <v>32867</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-3592</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-707.3726211353406</t>
+          <t>-611.1283719113699</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-477.4368452003091</t>
+          <t>-81.78500117953081</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>11478.0</t>
+          <t>20848.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-21.12</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.75</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,54 +10044,54 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.49</v>
+        <v>50.44</v>
       </c>
       <c r="AN23" t="n">
-        <v>53.34</v>
+        <v>53.16</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,17 +10100,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-124.61</t>
+          <t>-123.52</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>99533.07510729613</t>
+          <t>99414.84642857141</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6960.0</t>
+          <t>11478.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>23495.6</v>
+        <v>19367.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>18605.3</t>
+          <t>18899.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>34041.78</v>
+        <v>33340.5</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-749.1791258508009</t>
+          <t>-707.3726211353406</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-21.6738779014122</t>
+          <t>-477.4368452003091</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>6960.0</t>
+          <t>11478.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-17.00</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>150.32</t>
+          <t>152.58</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32.268</t>
+          <t>25.101</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-47.63</t>
+          <t>-54.87</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,32 +1029,32 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-104.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>845395.4</v>
+        <v>679118.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1614180.5</t>
+          <t>1504911.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1212910.14</v>
+        <v>1211030.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-768785</t>
+          <t>-825792</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>24849.04609468049</t>
+          <t>909.8040646425397</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-108939.7623917658</t>
+          <t>-130756.0271005662</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>32.268</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-52.42</t>
+          <t>-47.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>94.12</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN3" t="n">
         <v>25.15</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.09</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>762768.2</v>
+        <v>845395.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1603074.3</t>
+          <t>1614180.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1210877.9</v>
+        <v>1212910.14</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-840306</t>
+          <t>-768785</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>49174.2840013071</t>
+          <t>24849.04609468049</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-93015.5712937736</t>
+          <t>-108939.7623917658</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-52.42</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,42 +1879,42 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1925,24 +1925,24 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.09</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1358383.4</v>
+        <v>762768.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1676940.9</t>
+          <t>1603074.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1212587.6</v>
+        <v>1210877.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-318557</t>
+          <t>-840306</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>75026.98496404906</t>
+          <t>49174.2840013071</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-35389.88503614976</t>
+          <t>-93015.5712937736</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,127 +2173,127 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>31.352</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-19.00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-15.67</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,63 +2309,63 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.96</v>
+        <v>24.97</v>
       </c>
       <c r="AN5" t="n">
         <v>25.15</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1437406.4</v>
+        <v>1358383.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1217210.96</v>
+        <v>1212587.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,37 +2739,37 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>24.98</v>
+        <v>24.96</v>
       </c>
       <c r="AN6" t="n">
-        <v>25.16</v>
+        <v>25.15</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2330704.4</v>
+        <v>1437406.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1227934.96</v>
+        <v>1217210.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>25</v>
+        <v>24.98</v>
       </c>
       <c r="AN7" t="n">
-        <v>25.17</v>
+        <v>25.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2382965.6</v>
+        <v>2330704.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1217959.22</v>
+        <v>1227934.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>25.03</v>
+        <v>25</v>
       </c>
       <c r="AN8" t="n">
-        <v>25.18</v>
+        <v>25.17</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2443380.4</v>
+        <v>2382965.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1233866.56</v>
+        <v>1217959.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>326866.1581960404</t>
+          <t>158481.2602790978</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,39 +4039,39 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>25.08</v>
+        <v>25.03</v>
       </c>
       <c r="AN9" t="n">
-        <v>25.2</v>
+        <v>25.18</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1995498.4</v>
+        <v>2443380.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1183171.94</v>
+        <v>1233866.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>223952.9352846714</t>
+          <t>326866.1581960404</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>210.228</t>
+          <t>42.716</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,102 +4348,102 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-2.96</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>42.54</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,39 +4469,39 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>25.12</v>
+        <v>25.08</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.22</v>
+        <v>25.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-68.41</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1971587.4</v>
+        <v>1995498.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1383171.1</t>
+          <t>1447308.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1209715.2</v>
+        <v>1183171.94</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>588416</t>
+          <t>548190</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>21396.27799944613</t>
+          <t>52558.84065871156</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>330373.7262939773</t>
+          <t>223952.9352846714</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>210.228</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>25.14</v>
+        <v>25.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.24</v>
+        <v>25.22</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.04</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1097188.6</v>
+        <v>1971587.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1002558.1</t>
+          <t>1383171.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1151381.24</v>
+        <v>1209715.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>94630</t>
+          <t>588416</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-34781.43987228681</t>
+          <t>21396.27799944613</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>21726.90179677238</t>
+          <t>330373.7262939773</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,42 +5183,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>68.61</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>28.002</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5319,63 +5319,63 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>25.16</v>
+        <v>25.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.26</v>
+        <v>25.24</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-26.97</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.07</t>
+          <t>-103.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11845146.99156442</t>
+          <t>11828459.60719755</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>699699.0</t>
+          <t>1724881.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>902862.4</v>
+        <v>1097188.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>908805.3</t>
+          <t>1002558.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1262902.06</v>
+        <v>1151381.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5942</t>
+          <t>94630</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-45055.68381211576</t>
+          <t>-34781.43987228681</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-42950.34397769091</t>
+          <t>21726.90179677238</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>699699.0</t>
+          <t>1724881.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>53.74</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="AN13" t="n">
-        <v>51.13</v>
+        <v>50.95</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.51</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>12107.6</v>
+        <v>10386.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>13058.9</t>
+          <t>11531.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>18823.32</v>
+        <v>17989.48</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-951</t>
+          <t>-1145</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-836.8273699700007</t>
+          <t>-908.0103183348134</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-859.4840644606156</t>
+          <t>-1299.516534341283</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-21.95</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>53.74</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>48.87</v>
+        <v>48.78</v>
       </c>
       <c r="AN14" t="n">
-        <v>51.33</v>
+        <v>51.13</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-141.95</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>12674.8</v>
+        <v>12107.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>13088.5</t>
+          <t>13058.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>21902.1</v>
+        <v>18823.32</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-413</t>
+          <t>-951</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-832.7079709717071</t>
+          <t>-836.8273699700007</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-800.706105186071</t>
+          <t>-859.4840644606156</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-21.95</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-8.50</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.02999999999999</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>48.99</v>
+        <v>48.87</v>
       </c>
       <c r="AN15" t="n">
-        <v>51.52</v>
+        <v>51.33</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-24.50</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-140.30</t>
+          <t>-141.95</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>11302</v>
+        <v>12674.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>12352.4</t>
+          <t>13088.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>23372.88</v>
+        <v>21902.1</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1050</t>
+          <t>-413</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-838.5264920236409</t>
+          <t>-832.7079709717071</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1024.462373894361</t>
+          <t>-800.706105186071</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.02999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>49.16</v>
+        <v>48.99</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.72</v>
+        <v>51.52</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-29.79</t>
+          <t>-24.50</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,22 +7110,22 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-137.83</t>
+          <t>-140.30</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
@@ -7133,30 +7133,30 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12214.6</t>
+          <t>12352.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>23633.42</v>
+        <v>23372.88</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-1050</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-804.7199680471464</t>
+          <t>-838.5264920236409</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1331.954815838546</t>
+          <t>-1024.462373894361</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>49.36</v>
+        <v>49.16</v>
       </c>
       <c r="AN17" t="n">
-        <v>51.92</v>
+        <v>51.72</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-29.79</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>12677.4</v>
+        <v>11302</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>24098.68</v>
+        <v>23633.42</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>49.62</v>
+        <v>49.36</v>
       </c>
       <c r="AN18" t="n">
-        <v>52.16</v>
+        <v>51.92</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>14010.2</v>
+        <v>12677.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>24459.88</v>
+        <v>24098.68</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,54 +8324,54 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>49.81</v>
+        <v>49.62</v>
       </c>
       <c r="AN19" t="n">
-        <v>52.35</v>
+        <v>52.16</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8380,17 +8380,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>13502.2</v>
+        <v>14010.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>25275.3</v>
+        <v>24459.88</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1059.740935176555</t>
+          <t>-951.8336894428303</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-28.52</t>
+          <t>-27.01</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,34 +8774,34 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>50.04</v>
+        <v>49.81</v>
       </c>
       <c r="AN20" t="n">
-        <v>52.56</v>
+        <v>52.35</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>13402.8</v>
+        <v>13502.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>28099.9</v>
+        <v>25275.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-473.081967111284</t>
+          <t>-1059.740935176555</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-28.76</t>
+          <t>-28.52</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,34 +9204,34 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>50.18</v>
+        <v>50.04</v>
       </c>
       <c r="AN21" t="n">
-        <v>52.81</v>
+        <v>52.56</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-29.28</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-124.89</t>
+          <t>-126.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>13127.2</v>
+        <v>13402.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>18427.5</t>
+          <t>18750.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>31635.06</v>
+        <v>28099.9</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-5300</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-575.2561739766202</t>
+          <t>-559.5370652281069</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-377.9590853354966</t>
+          <t>-473.081967111284</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-22.77</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-28.76</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-16.14</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,60 +9629,60 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.3</v>
+        <v>50.18</v>
       </c>
       <c r="AN22" t="n">
-        <v>53</v>
+        <v>52.81</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
           <t>-0.79</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-124.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>15436</v>
+        <v>13127.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>19028.5</t>
+          <t>18427.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>32867</v>
+        <v>31635.06</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-3592</t>
+          <t>-5300</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-611.1283719113699</t>
+          <t>-575.2561739766202</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-81.78500117953081</t>
+          <t>-377.9590853354966</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-21.12</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-16.14</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,17 +10059,17 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -10079,38 +10079,38 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.44</v>
+        <v>50.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>53.16</v>
+        <v>53</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>53.81</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-123.52</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/10/31</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>99414.84642857141</t>
+          <t>99284.96148359487</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>11478.0</t>
+          <t>20848.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>19367.4</v>
+        <v>15436</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>18899.4</t>
+          <t>19028.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>33340.5</v>
+        <v>32867</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>-3592</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-707.3726211353406</t>
+          <t>-611.1283719113699</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-477.4368452003091</t>
+          <t>-81.78500117953081</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>11478.0</t>
+          <t>20848.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-21.12</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>152.58</t>
+          <t>151.77</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -883,99 +883,99 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>55.296</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>25.101</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-28.35</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-54.87</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>94.12</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,27 +1034,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>65.81</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.74</t>
+          <t>-104.07</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>679118.4</v>
+        <v>802395.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1504911.4</t>
+          <t>1119901.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1211030.44</v>
+        <v>1231337.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-825792</t>
+          <t>-317505</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>909.8040646425397</t>
+          <t>-12406.86759441208</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-130756.0271005662</t>
+          <t>-85648.56171921245</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,22 +1211,22 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>11.98</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.268</t>
+          <t>25.101</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-47.63</t>
+          <t>-54.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,32 +1459,32 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -1495,22 +1495,22 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-104.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>845395.4</v>
+        <v>679118.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1614180.5</t>
+          <t>1504911.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1212910.14</v>
+        <v>1211030.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-768785</t>
+          <t>-825792</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>24849.04609468049</t>
+          <t>909.8040646425397</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-108939.7623917658</t>
+          <t>-130756.0271005662</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>32.268</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-52.42</t>
+          <t>-47.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>94.12</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN4" t="n">
         <v>25.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.09</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>762768.2</v>
+        <v>845395.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1603074.3</t>
+          <t>1614180.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1210877.9</v>
+        <v>1212910.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-840306</t>
+          <t>-768785</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>49174.2840013071</t>
+          <t>24849.04609468049</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-93015.5712937736</t>
+          <t>-108939.7623917658</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-52.42</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,42 +2309,42 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -2355,24 +2355,24 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.09</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1358383.4</v>
+        <v>762768.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1676940.9</t>
+          <t>1603074.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1212587.6</v>
+        <v>1210877.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-318557</t>
+          <t>-840306</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>75026.98496404906</t>
+          <t>49174.2840013071</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-35389.88503614976</t>
+          <t>-93015.5712937736</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31.352</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,102 +2628,102 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-19.00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-15.67</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,63 +2739,63 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>24.96</v>
+        <v>24.97</v>
       </c>
       <c r="AN6" t="n">
         <v>25.15</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1437406.4</v>
+        <v>1358383.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1217210.96</v>
+        <v>1212587.6</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,37 +3169,37 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>24.98</v>
+        <v>24.96</v>
       </c>
       <c r="AN7" t="n">
-        <v>25.16</v>
+        <v>25.15</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2330704.4</v>
+        <v>1437406.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1227934.96</v>
+        <v>1217210.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>25</v>
+        <v>24.98</v>
       </c>
       <c r="AN8" t="n">
-        <v>25.17</v>
+        <v>25.16</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2382965.6</v>
+        <v>2330704.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1217959.22</v>
+        <v>1227934.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>25.03</v>
+        <v>25</v>
       </c>
       <c r="AN9" t="n">
-        <v>25.18</v>
+        <v>25.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2443380.4</v>
+        <v>2382965.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1233866.56</v>
+        <v>1217959.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>326866.1581960404</t>
+          <t>158481.2602790978</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,39 +4469,39 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>25.08</v>
+        <v>25.03</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.2</v>
+        <v>25.18</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1995498.4</v>
+        <v>2443380.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1183171.94</v>
+        <v>1233866.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>223952.9352846714</t>
+          <t>326866.1581960404</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>210.228</t>
+          <t>42.716</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,102 +4778,102 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-2.96</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>42.54</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,39 +4899,39 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>25.12</v>
+        <v>25.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.22</v>
+        <v>25.2</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-68.41</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1971587.4</v>
+        <v>1995498.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1383171.1</t>
+          <t>1447308.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1209715.2</v>
+        <v>1183171.94</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>588416</t>
+          <t>548190</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>21396.27799944613</t>
+          <t>52558.84065871156</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>330373.7262939773</t>
+          <t>223952.9352846714</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>210.228</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>25.14</v>
+        <v>25.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.24</v>
+        <v>25.22</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>-33.35</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.04</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11828459.60719755</t>
+          <t>11813569.73623853</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1097188.6</v>
+        <v>1971587.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1002558.1</t>
+          <t>1383171.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1151381.24</v>
+        <v>1209715.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>94630</t>
+          <t>588416</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-34781.43987228681</t>
+          <t>21396.27799944613</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>21726.90179677238</t>
+          <t>330373.7262939773</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1724881.0</t>
+          <t>5243760.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.37</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>48.64</v>
+        <v>48.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>50.95</v>
+        <v>50.76</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-142.51</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>10386.2</v>
+        <v>11051</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>11531.8</t>
+          <t>11176.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>17989.48</v>
+        <v>17175.12</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1145</t>
+          <t>-125</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-908.0103183348134</t>
+          <t>-963.9127847293369</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1299.516534341283</t>
+          <t>-1271.376349899216</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,68 +6174,68 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>53.74</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="AN14" t="n">
-        <v>51.13</v>
+        <v>50.95</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.51</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>12107.6</v>
+        <v>10386.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>13058.9</t>
+          <t>11531.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>18823.32</v>
+        <v>17989.48</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-951</t>
+          <t>-1145</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-836.8273699700007</t>
+          <t>-908.0103183348134</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-859.4840644606156</t>
+          <t>-1299.516534341283</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-21.95</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>53.74</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>48.87</v>
+        <v>48.78</v>
       </c>
       <c r="AN15" t="n">
-        <v>51.33</v>
+        <v>51.13</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-141.95</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>12674.8</v>
+        <v>12107.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>13088.5</t>
+          <t>13058.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>21902.1</v>
+        <v>18823.32</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-413</t>
+          <t>-951</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-832.7079709717071</t>
+          <t>-836.8273699700007</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-800.706105186071</t>
+          <t>-859.4840644606156</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-21.95</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-8.50</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.02999999999999</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>48.99</v>
+        <v>48.87</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.52</v>
+        <v>51.33</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-24.50</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-140.30</t>
+          <t>-141.95</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>11302</v>
+        <v>12674.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12352.4</t>
+          <t>13088.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>23372.88</v>
+        <v>21902.1</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1050</t>
+          <t>-413</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-838.5264920236409</t>
+          <t>-832.7079709717071</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1024.462373894361</t>
+          <t>-800.706105186071</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.02999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>49.16</v>
+        <v>48.99</v>
       </c>
       <c r="AN17" t="n">
-        <v>51.72</v>
+        <v>51.52</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-29.79</t>
+          <t>-24.50</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-137.83</t>
+          <t>-140.30</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
@@ -7563,30 +7563,30 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>12214.6</t>
+          <t>12352.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>23633.42</v>
+        <v>23372.88</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-1050</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-804.7199680471464</t>
+          <t>-838.5264920236409</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1331.954815838546</t>
+          <t>-1024.462373894361</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>49.36</v>
+        <v>49.16</v>
       </c>
       <c r="AN18" t="n">
-        <v>51.92</v>
+        <v>51.72</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-29.79</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>12677.4</v>
+        <v>11302</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>24098.68</v>
+        <v>23633.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>49.62</v>
+        <v>49.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>52.16</v>
+        <v>51.92</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>14010.2</v>
+        <v>12677.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>24459.88</v>
+        <v>24098.68</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,54 +8754,54 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>49.81</v>
+        <v>49.62</v>
       </c>
       <c r="AN20" t="n">
-        <v>52.35</v>
+        <v>52.16</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8810,17 +8810,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>13502.2</v>
+        <v>14010.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>25275.3</v>
+        <v>24459.88</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1059.740935176555</t>
+          <t>-951.8336894428303</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-28.52</t>
+          <t>-27.01</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,34 +9204,34 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>50.04</v>
+        <v>49.81</v>
       </c>
       <c r="AN21" t="n">
-        <v>52.56</v>
+        <v>52.35</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>13402.8</v>
+        <v>13502.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>28099.9</v>
+        <v>25275.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-473.081967111284</t>
+          <t>-1059.740935176555</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-28.76</t>
+          <t>-28.52</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,34 +9634,34 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.18</v>
+        <v>50.04</v>
       </c>
       <c r="AN22" t="n">
-        <v>52.81</v>
+        <v>52.56</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-29.28</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-124.89</t>
+          <t>-126.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>13127.2</v>
+        <v>13402.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18427.5</t>
+          <t>18750.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>31635.06</v>
+        <v>28099.9</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-5300</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-575.2561739766202</t>
+          <t>-559.5370652281069</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-377.9590853354966</t>
+          <t>-473.081967111284</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-22.77</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-28.76</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-16.14</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,60 +10059,60 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.3</v>
+        <v>50.18</v>
       </c>
       <c r="AN23" t="n">
-        <v>53</v>
+        <v>52.81</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.82</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-17.77</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>-0.79</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-124.89</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>99284.96148359487</t>
+          <t>99164.09829059828</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>15436</v>
+        <v>13127.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>19028.5</t>
+          <t>18427.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>32867</v>
+        <v>31635.06</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3592</t>
+          <t>-5300</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-611.1283719113699</t>
+          <t>-575.2561739766202</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-81.78500117953081</t>
+          <t>-377.9590853354966</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>20848.0</t>
+          <t>13179.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-21.12</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>151.77</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.296</t>
+          <t>41.241</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,58 +1019,58 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>24.98</v>
+        <v>24.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.15</v>
+        <v>25.14</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>65.81</t>
+          <t>61.49</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.07</t>
+          <t>-103.53</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>802395.6</v>
+        <v>877200.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1119901.0</t>
+          <t>1117792.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1231337.2</v>
+        <v>1238747.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-317505</t>
+          <t>-240591</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12406.86759441208</t>
+          <t>-22647.3951813155</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-85648.56171921245</t>
+          <t>-78970.29690928431</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,99 +1313,99 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>55.296</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>25.101</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-28.35</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-54.87</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>94.12</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,27 +1464,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>65.81</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.74</t>
+          <t>-104.07</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>679118.4</v>
+        <v>802395.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1504911.4</t>
+          <t>1119901.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1211030.44</v>
+        <v>1231337.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-825792</t>
+          <t>-317505</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>909.8040646425397</t>
+          <t>-12406.86759441208</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-130756.0271005662</t>
+          <t>-85648.56171921245</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,22 +1641,22 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>11.98</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32.268</t>
+          <t>25.101</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-47.63</t>
+          <t>-54.87</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,32 +1889,32 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1925,22 +1925,22 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-104.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>845395.4</v>
+        <v>679118.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1614180.5</t>
+          <t>1504911.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1212910.14</v>
+        <v>1211030.44</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-768785</t>
+          <t>-825792</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>24849.04609468049</t>
+          <t>909.8040646425397</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-108939.7623917658</t>
+          <t>-130756.0271005662</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,42 +2173,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>32.268</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>-0.6</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>20.57</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>25.05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-52.42</t>
+          <t>-47.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>94.12</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN5" t="n">
         <v>25.15</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.09</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>762768.2</v>
+        <v>845395.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1603074.3</t>
+          <t>1614180.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1210877.9</v>
+        <v>1212910.14</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-840306</t>
+          <t>-768785</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>49174.2840013071</t>
+          <t>24849.04609468049</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-93015.5712937736</t>
+          <t>-108939.7623917658</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-52.42</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,42 +2739,42 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -2785,24 +2785,24 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.09</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1358383.4</v>
+        <v>762768.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1676940.9</t>
+          <t>1603074.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1212587.6</v>
+        <v>1210877.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-318557</t>
+          <t>-840306</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>75026.98496404906</t>
+          <t>49174.2840013071</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-35389.88503614976</t>
+          <t>-93015.5712937736</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31.352</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>-19.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,63 +3169,63 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>24.96</v>
+        <v>24.97</v>
       </c>
       <c r="AN7" t="n">
         <v>25.15</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1437406.4</v>
+        <v>1358383.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1217210.96</v>
+        <v>1212587.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,37 +3599,37 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>24.98</v>
+        <v>24.96</v>
       </c>
       <c r="AN8" t="n">
-        <v>25.16</v>
+        <v>25.15</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2330704.4</v>
+        <v>1437406.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1227934.96</v>
+        <v>1217210.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>25</v>
+        <v>24.98</v>
       </c>
       <c r="AN9" t="n">
-        <v>25.17</v>
+        <v>25.16</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2382965.6</v>
+        <v>2330704.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1217959.22</v>
+        <v>1227934.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>25.03</v>
+        <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.18</v>
+        <v>25.17</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2443380.4</v>
+        <v>2382965.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1233866.56</v>
+        <v>1217959.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>326866.1581960404</t>
+          <t>158481.2602790978</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,39 +4899,39 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>25.08</v>
+        <v>25.03</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.2</v>
+        <v>25.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1995498.4</v>
+        <v>2443380.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1183171.94</v>
+        <v>1233866.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>223952.9352846714</t>
+          <t>326866.1581960404</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>210.228</t>
+          <t>42.716</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,39 +5329,39 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>25.12</v>
+        <v>25.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.22</v>
+        <v>25.2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-33.35</t>
+          <t>-68.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.00</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11813569.73623853</t>
+          <t>11797899.73740458</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1971587.4</v>
+        <v>1995498.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1383171.1</t>
+          <t>1447308.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1209715.2</v>
+        <v>1183171.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>588416</t>
+          <t>548190</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>21396.27799944613</t>
+          <t>52558.84065871156</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>330373.7262939773</t>
+          <t>223952.9352846714</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>5243760.0</t>
+          <t>1054237.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,70 +5749,70 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>51.45</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>48.36</v>
+        <v>48.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>50.76</v>
+        <v>50.56</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>53.18</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>-1.36</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.66</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>11051</v>
+        <v>9145.200000000001</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>11176.5</t>
+          <t>10223.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>17175.12</v>
+        <v>16628.22</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-125</t>
+          <t>-1078</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-963.9127847293369</t>
+          <t>-1056.440635085176</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1271.376349899216</t>
+          <t>-1565.343812042289</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,63 +6179,63 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>48.64</v>
+        <v>48.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>50.95</v>
+        <v>50.76</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-142.51</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>10386.2</v>
+        <v>11051</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>11531.8</t>
+          <t>11176.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>17989.48</v>
+        <v>17175.12</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1145</t>
+          <t>-125</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-908.0103183348134</t>
+          <t>-963.9127847293369</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1299.516534341283</t>
+          <t>-1271.376349899216</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,63 +6609,63 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>53.74</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="AN15" t="n">
-        <v>51.13</v>
+        <v>50.95</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.51</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>12107.6</v>
+        <v>10386.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>13058.9</t>
+          <t>11531.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>18823.32</v>
+        <v>17989.48</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-951</t>
+          <t>-1145</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-836.8273699700007</t>
+          <t>-908.0103183348134</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-859.4840644606156</t>
+          <t>-1299.516534341283</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-21.95</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>53.74</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>48.87</v>
+        <v>48.78</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.33</v>
+        <v>51.13</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-141.95</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>12674.8</v>
+        <v>12107.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>13088.5</t>
+          <t>13058.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>21902.1</v>
+        <v>18823.32</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-413</t>
+          <t>-951</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-832.7079709717071</t>
+          <t>-836.8273699700007</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-800.706105186071</t>
+          <t>-859.4840644606156</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-21.95</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-8.50</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.02999999999999</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>48.99</v>
+        <v>48.87</v>
       </c>
       <c r="AN17" t="n">
-        <v>51.52</v>
+        <v>51.33</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-24.50</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-140.30</t>
+          <t>-141.95</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>11302</v>
+        <v>12674.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>12352.4</t>
+          <t>13088.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>23372.88</v>
+        <v>21902.1</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1050</t>
+          <t>-413</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-838.5264920236409</t>
+          <t>-832.7079709717071</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1024.462373894361</t>
+          <t>-800.706105186071</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.02999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>49.16</v>
+        <v>48.99</v>
       </c>
       <c r="AN18" t="n">
-        <v>51.72</v>
+        <v>51.52</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-29.79</t>
+          <t>-24.50</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-137.83</t>
+          <t>-140.30</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
@@ -7993,30 +7993,30 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>12214.6</t>
+          <t>12352.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>23633.42</v>
+        <v>23372.88</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-1050</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-804.7199680471464</t>
+          <t>-838.5264920236409</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1331.954815838546</t>
+          <t>-1024.462373894361</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>49.36</v>
+        <v>49.16</v>
       </c>
       <c r="AN19" t="n">
-        <v>51.92</v>
+        <v>51.72</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-29.79</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>12677.4</v>
+        <v>11302</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>24098.68</v>
+        <v>23633.42</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>49.62</v>
+        <v>49.36</v>
       </c>
       <c r="AN20" t="n">
-        <v>52.16</v>
+        <v>51.92</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>14010.2</v>
+        <v>12677.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>24459.88</v>
+        <v>24098.68</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,49 +9189,49 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>49.81</v>
+        <v>49.62</v>
       </c>
       <c r="AN21" t="n">
-        <v>52.35</v>
+        <v>52.16</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>13502.2</v>
+        <v>14010.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>25275.3</v>
+        <v>24459.88</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1059.740935176555</t>
+          <t>-951.8336894428303</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-28.52</t>
+          <t>-27.01</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-18.86</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,34 +9634,34 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>50.04</v>
+        <v>49.81</v>
       </c>
       <c r="AN22" t="n">
-        <v>52.56</v>
+        <v>52.35</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>13402.8</v>
+        <v>13502.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>28099.9</v>
+        <v>25275.3</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-473.081967111284</t>
+          <t>-1059.740935176555</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>312.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-28.76</t>
+          <t>-28.52</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,34 +10064,34 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.18</v>
+        <v>50.04</v>
       </c>
       <c r="AN23" t="n">
-        <v>52.81</v>
+        <v>52.56</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,17 +10100,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-17.77</t>
+          <t>-29.28</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-124.89</t>
+          <t>-126.86</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>99164.09829059828</t>
+          <t>99033.75106685635</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>13127.2</v>
+        <v>13402.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>18427.5</t>
+          <t>18750.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>31635.06</v>
+        <v>28099.9</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-5300</t>
+          <t>-5348</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-575.2561739766202</t>
+          <t>-559.5370652281069</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-377.9590853354966</t>
+          <t>-473.081967111284</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>13179.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-22.77</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>147.9</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.241</t>
+          <t>48.098</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.14</v>
+        <v>25.13</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>61.49</t>
+          <t>75.35</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.53</t>
+          <t>-102.97</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1033147.0</t>
+          <t>1209308.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>877200.6</v>
+        <v>1015812.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1117792.0</t>
+          <t>889290.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1238747.06</v>
+        <v>1235178.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-240591</t>
+          <t>126522</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-22647.3951813155</t>
+          <t>-28256.90040259043</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-78970.29690928431</t>
+          <t>-59109.17911960254</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1033147.0</t>
+          <t>1209308.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>55.296</t>
+          <t>41.241</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,58 +1449,58 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>24.98</v>
+        <v>24.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>25.15</v>
+        <v>25.14</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>65.81</t>
+          <t>61.49</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.07</t>
+          <t>-103.53</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>802395.6</v>
+        <v>877200.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1119901.0</t>
+          <t>1117792.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1231337.2</v>
+        <v>1238747.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-317505</t>
+          <t>-240591</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12406.86759441208</t>
+          <t>-22647.3951813155</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-85648.56171921245</t>
+          <t>-78970.29690928431</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,99 +1743,99 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>55.296</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>25.101</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-28.35</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-54.87</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>94.12</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1894,27 +1894,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>65.81</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.74</t>
+          <t>-104.07</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>679118.4</v>
+        <v>802395.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1504911.4</t>
+          <t>1119901.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1211030.44</v>
+        <v>1231337.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-825792</t>
+          <t>-317505</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>909.8040646425397</t>
+          <t>-12406.86759441208</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-130756.0271005662</t>
+          <t>-85648.56171921245</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,22 +2071,22 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32.268</t>
+          <t>25.101</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-47.63</t>
+          <t>-54.87</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,32 +2319,32 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -2355,22 +2355,22 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-104.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>845395.4</v>
+        <v>679118.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1614180.5</t>
+          <t>1504911.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1212910.14</v>
+        <v>1211030.44</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-768785</t>
+          <t>-825792</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>24849.04609468049</t>
+          <t>909.8040646425397</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-108939.7623917658</t>
+          <t>-130756.0271005662</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>32.268</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-52.42</t>
+          <t>-47.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>94.12</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN6" t="n">
         <v>25.15</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.09</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>762768.2</v>
+        <v>845395.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1603074.3</t>
+          <t>1614180.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1210877.9</v>
+        <v>1212910.14</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-840306</t>
+          <t>-768785</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>49174.2840013071</t>
+          <t>24849.04609468049</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-93015.5712937736</t>
+          <t>-108939.7623917658</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-52.42</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,42 +3169,42 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM7" t="n">
@@ -3215,24 +3215,24 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.09</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1358383.4</v>
+        <v>762768.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1676940.9</t>
+          <t>1603074.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1212587.6</v>
+        <v>1210877.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-318557</t>
+          <t>-840306</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>75026.98496404906</t>
+          <t>49174.2840013071</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-35389.88503614976</t>
+          <t>-93015.5712937736</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31.352</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>-19.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,63 +3599,63 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>24.96</v>
+        <v>24.97</v>
       </c>
       <c r="AN8" t="n">
         <v>25.15</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1437406.4</v>
+        <v>1358383.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1217210.96</v>
+        <v>1212587.6</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,37 +4029,37 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>24.98</v>
+        <v>24.96</v>
       </c>
       <c r="AN9" t="n">
-        <v>25.16</v>
+        <v>25.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2330704.4</v>
+        <v>1437406.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1227934.96</v>
+        <v>1217210.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>25</v>
+        <v>24.98</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.17</v>
+        <v>25.16</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2382965.6</v>
+        <v>2330704.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1217959.22</v>
+        <v>1227934.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>25.03</v>
+        <v>25</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.18</v>
+        <v>25.17</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2443380.4</v>
+        <v>2382965.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1233866.56</v>
+        <v>1217959.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>326866.1581960404</t>
+          <t>158481.2602790978</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.716</t>
+          <t>141.867</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,39 +5329,39 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>25.08</v>
+        <v>25.03</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.2</v>
+        <v>25.18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-68.41</t>
+          <t>-91.57</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-105.18</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11797899.73740458</t>
+          <t>11782680.32012195</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1995498.4</v>
+        <v>2443380.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1447308.3</t>
+          <t>1691656.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1183171.94</v>
+        <v>1233866.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>548190</t>
+          <t>751723</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>52558.84065871156</t>
+          <t>94759.96643368524</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>223952.9352846714</t>
+          <t>326866.1581960404</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1054237.0</t>
+          <t>3494325.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,53 +5759,53 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>51.45</t>
+          <t>31.16</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>48.12</v>
+        <v>47.86</v>
       </c>
       <c r="AN13" t="n">
-        <v>50.56</v>
+        <v>50.34</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.18</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-142.66</t>
+          <t>-142.70</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>5020.0</t>
+          <t>4019.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>9145.200000000001</v>
+        <v>7084.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>10223.6</t>
+          <t>9879.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>16628.22</v>
+        <v>15702.14</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1078</t>
+          <t>-2794</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-1056.440635085176</t>
+          <t>-1171.920912801515</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1565.343812042289</t>
+          <t>-1807.062440241383</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>5020.0</t>
+          <t>4019.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,70 +6179,70 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>51.45</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>48.36</v>
+        <v>48.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>50.76</v>
+        <v>50.56</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>53.18</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
           <t>-1.36</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.66</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>11051</v>
+        <v>9145.200000000001</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>11176.5</t>
+          <t>10223.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>17175.12</v>
+        <v>16628.22</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-125</t>
+          <t>-1078</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-963.9127847293369</t>
+          <t>-1056.440635085176</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1271.376349899216</t>
+          <t>-1565.343812042289</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,63 +6609,63 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>48.64</v>
+        <v>48.36</v>
       </c>
       <c r="AN15" t="n">
-        <v>50.95</v>
+        <v>50.76</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-142.51</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>10386.2</v>
+        <v>11051</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>11531.8</t>
+          <t>11176.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>17989.48</v>
+        <v>17175.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1145</t>
+          <t>-125</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-908.0103183348134</t>
+          <t>-963.9127847293369</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1299.516534341283</t>
+          <t>-1271.376349899216</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,63 +7039,63 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>53.74</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.13</v>
+        <v>50.95</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.51</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>12107.6</v>
+        <v>10386.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>13058.9</t>
+          <t>11531.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>18823.32</v>
+        <v>17989.48</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-951</t>
+          <t>-1145</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-836.8273699700007</t>
+          <t>-908.0103183348134</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-859.4840644606156</t>
+          <t>-1299.516534341283</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-21.95</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>53.74</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>48.87</v>
+        <v>48.78</v>
       </c>
       <c r="AN17" t="n">
-        <v>51.33</v>
+        <v>51.13</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-141.95</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>12674.8</v>
+        <v>12107.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>13088.5</t>
+          <t>13058.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>21902.1</v>
+        <v>18823.32</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-413</t>
+          <t>-951</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-832.7079709717071</t>
+          <t>-836.8273699700007</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-800.706105186071</t>
+          <t>-859.4840644606156</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-21.95</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-8.50</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>46.02999999999999</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>48.99</v>
+        <v>48.87</v>
       </c>
       <c r="AN18" t="n">
-        <v>51.52</v>
+        <v>51.33</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-24.50</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-140.30</t>
+          <t>-141.95</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>11302</v>
+        <v>12674.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>12352.4</t>
+          <t>13088.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>23372.88</v>
+        <v>21902.1</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1050</t>
+          <t>-413</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-838.5264920236409</t>
+          <t>-832.7079709717071</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1024.462373894361</t>
+          <t>-800.706105186071</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.02999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>49.16</v>
+        <v>48.99</v>
       </c>
       <c r="AN19" t="n">
-        <v>51.72</v>
+        <v>51.52</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-29.79</t>
+          <t>-24.50</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-137.83</t>
+          <t>-140.30</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
@@ -8423,30 +8423,30 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12214.6</t>
+          <t>12352.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>23633.42</v>
+        <v>23372.88</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-1050</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-804.7199680471464</t>
+          <t>-838.5264920236409</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1331.954815838546</t>
+          <t>-1024.462373894361</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>49.36</v>
+        <v>49.16</v>
       </c>
       <c r="AN20" t="n">
-        <v>51.92</v>
+        <v>51.72</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-29.79</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>12677.4</v>
+        <v>11302</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>24098.68</v>
+        <v>23633.42</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>49.62</v>
+        <v>49.36</v>
       </c>
       <c r="AN21" t="n">
-        <v>52.16</v>
+        <v>51.92</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>14010.2</v>
+        <v>12677.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>24459.88</v>
+        <v>24098.68</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,49 +9619,49 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>49.81</v>
+        <v>49.62</v>
       </c>
       <c r="AN22" t="n">
-        <v>52.35</v>
+        <v>52.16</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>13502.2</v>
+        <v>14010.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>25275.3</v>
+        <v>24459.88</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1059.740935176555</t>
+          <t>-951.8336894428303</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>312.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,102 +9938,102 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-27.01</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-05-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-05-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>54.8</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>54.8</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-18.86</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>6.57</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>-1.51</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-28.52</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-05-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-05-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>54.8</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>54.8</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>-17.89</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>6.57</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>-0.09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,34 +10064,34 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>50.04</v>
+        <v>49.81</v>
       </c>
       <c r="AN23" t="n">
-        <v>52.56</v>
+        <v>52.35</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,17 +10100,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-29.28</t>
+          <t>-35.50</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-126.86</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>99033.75106685635</t>
+          <t>98901.64133522726</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>13402.8</v>
+        <v>13502.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>18750.9</t>
+          <t>18498.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>28099.9</v>
+        <v>25275.3</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-5348</t>
+          <t>-4996</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-559.5370652281069</t>
+          <t>-636.4915067586373</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-473.081967111284</t>
+          <t>-1059.740935176555</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>7457.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48.098</t>
+          <t>69.002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>17.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,37 +1019,37 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1061,26 +1061,26 @@
         <v>24.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>25.13</v>
+        <v>25.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>75.35</t>
+          <t>102.58</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.97</t>
+          <t>-102.36</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1209308.0</t>
+          <t>1735650.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1015812.4</v>
+        <v>1200790.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>889290.3</t>
+          <t>1023092.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1235178.18</v>
+        <v>1253611.68</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>126522</t>
+          <t>177697</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-28256.90040259043</t>
+          <t>-24563.99529278192</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-59109.17911960254</t>
+          <t>-4253.017188835191</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1209308.0</t>
+          <t>1735650.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>25.1</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.241</t>
+          <t>48.098</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>25.14</v>
+        <v>25.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>61.49</t>
+          <t>75.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.53</t>
+          <t>-102.97</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1033147.0</t>
+          <t>1209308.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>877200.6</v>
+        <v>1015812.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1117792.0</t>
+          <t>889290.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1238747.06</v>
+        <v>1235178.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-240591</t>
+          <t>126522</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-22647.3951813155</t>
+          <t>-28256.90040259043</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-78970.29690928431</t>
+          <t>-59109.17911960254</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1033147.0</t>
+          <t>1209308.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55.296</t>
+          <t>41.241</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,58 +1879,58 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>24.98</v>
+        <v>24.97</v>
       </c>
       <c r="AN4" t="n">
-        <v>25.15</v>
+        <v>25.14</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>65.81</t>
+          <t>61.49</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.07</t>
+          <t>-103.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>802395.6</v>
+        <v>877200.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1119901.0</t>
+          <t>1117792.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1231337.2</v>
+        <v>1238747.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-317505</t>
+          <t>-240591</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12406.86759441208</t>
+          <t>-22647.3951813155</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-85648.56171921245</t>
+          <t>-78970.29690928431</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,99 +2173,99 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>55.296</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>25.101</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-28.35</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-54.87</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>94.12</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2324,27 +2324,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>65.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.74</t>
+          <t>-104.07</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>679118.4</v>
+        <v>802395.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1504911.4</t>
+          <t>1119901.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1211030.44</v>
+        <v>1231337.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-825792</t>
+          <t>-317505</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>909.8040646425397</t>
+          <t>-12406.86759441208</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-130756.0271005662</t>
+          <t>-85648.56171921245</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,22 +2501,22 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>11.93</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.268</t>
+          <t>25.101</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-47.63</t>
+          <t>-54.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,32 +2749,32 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -2785,22 +2785,22 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-104.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>845395.4</v>
+        <v>679118.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1614180.5</t>
+          <t>1504911.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1212910.14</v>
+        <v>1211030.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-768785</t>
+          <t>-825792</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>24849.04609468049</t>
+          <t>909.8040646425397</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-108939.7623917658</t>
+          <t>-130756.0271005662</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>32.268</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-52.42</t>
+          <t>-47.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>94.12</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN7" t="n">
         <v>25.15</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.09</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>762768.2</v>
+        <v>845395.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1603074.3</t>
+          <t>1614180.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1210877.9</v>
+        <v>1212910.14</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-840306</t>
+          <t>-768785</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>49174.2840013071</t>
+          <t>24849.04609468049</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-93015.5712937736</t>
+          <t>-108939.7623917658</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-52.42</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,42 +3599,42 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM8" t="n">
@@ -3645,24 +3645,24 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.08</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.09</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1358383.4</v>
+        <v>762768.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1676940.9</t>
+          <t>1603074.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1212587.6</v>
+        <v>1210877.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-318557</t>
+          <t>-840306</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>75026.98496404906</t>
+          <t>49174.2840013071</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-35389.88503614976</t>
+          <t>-93015.5712937736</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,34 +3893,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>31.352</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>-19.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,63 +4029,63 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>24.96</v>
+        <v>24.97</v>
       </c>
       <c r="AN9" t="n">
         <v>25.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1437406.4</v>
+        <v>1358383.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1217210.96</v>
+        <v>1212587.6</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,37 +4459,37 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>24.98</v>
+        <v>24.96</v>
       </c>
       <c r="AN10" t="n">
-        <v>25.16</v>
+        <v>25.15</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2330704.4</v>
+        <v>1437406.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1227934.96</v>
+        <v>1217210.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>25</v>
+        <v>24.98</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.17</v>
+        <v>25.16</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2382965.6</v>
+        <v>2330704.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1217959.22</v>
+        <v>1227934.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>141.867</t>
+          <t>16.003</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>25.03</v>
+        <v>25</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.18</v>
+        <v>25.17</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-91.57</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.18</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11782680.32012195</t>
+          <t>11768708.92694064</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2443380.4</v>
+        <v>2382965.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1691656.5</t>
+          <t>1642914.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1233866.56</v>
+        <v>1217959.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>751723</t>
+          <t>740051</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>94759.96643368524</t>
+          <t>104563.2424099026</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>326866.1581960404</t>
+          <t>158481.2602790978</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3494325.0</t>
+          <t>397625.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>45.9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>45.65</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-35.04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>31.16</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.02</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>47.86</v>
+        <v>47.52</v>
       </c>
       <c r="AN13" t="n">
-        <v>50.34</v>
+        <v>50.15</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-142.70</t>
+          <t>-142.47</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4019.0</t>
+          <t>4879.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>7084.8</v>
+        <v>5824.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9879.8</t>
+          <t>8965.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>15702.14</v>
+        <v>15289.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2794</t>
+          <t>-3141</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-1171.920912801515</t>
+          <t>-1278.792913751238</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1807.062440241383</t>
+          <t>-1866.588918974714</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>4019.0</t>
+          <t>4879.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-24.26</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>46.4</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>45.9</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,53 +6189,53 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>51.45</t>
+          <t>31.16</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>48.12</v>
+        <v>47.86</v>
       </c>
       <c r="AN14" t="n">
-        <v>50.56</v>
+        <v>50.34</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.18</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-142.66</t>
+          <t>-142.70</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>5020.0</t>
+          <t>4019.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>9145.200000000001</v>
+        <v>7084.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>10223.6</t>
+          <t>9879.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>16628.22</v>
+        <v>15702.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1078</t>
+          <t>-2794</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-1056.440635085176</t>
+          <t>-1171.920912801515</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1565.343812042289</t>
+          <t>-1807.062440241383</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>5020.0</t>
+          <t>4019.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,75 +6604,75 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>51.45</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>48.36</v>
+        <v>48.12</v>
       </c>
       <c r="AN15" t="n">
-        <v>50.76</v>
+        <v>50.56</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>53.18</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>-1.36</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>3.19</t>
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.66</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>11051</v>
+        <v>9145.200000000001</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>11176.5</t>
+          <t>10223.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>17175.12</v>
+        <v>16628.22</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-125</t>
+          <t>-1078</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-963.9127847293369</t>
+          <t>-1056.440635085176</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1271.376349899216</t>
+          <t>-1565.343812042289</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,68 +7034,68 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>48.64</v>
+        <v>48.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>50.95</v>
+        <v>50.76</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-142.51</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>10386.2</v>
+        <v>11051</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11531.8</t>
+          <t>11176.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>17989.48</v>
+        <v>17175.12</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1145</t>
+          <t>-125</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-908.0103183348134</t>
+          <t>-963.9127847293369</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1299.516534341283</t>
+          <t>-1271.376349899216</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,68 +7464,68 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>53.74</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="AN17" t="n">
-        <v>51.13</v>
+        <v>50.95</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.51</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>12107.6</v>
+        <v>10386.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>13058.9</t>
+          <t>11531.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>18823.32</v>
+        <v>17989.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-951</t>
+          <t>-1145</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-836.8273699700007</t>
+          <t>-908.0103183348134</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-859.4840644606156</t>
+          <t>-1299.516534341283</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-21.95</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>53.74</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>48.87</v>
+        <v>48.78</v>
       </c>
       <c r="AN18" t="n">
-        <v>51.33</v>
+        <v>51.13</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-141.95</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>12674.8</v>
+        <v>12107.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13088.5</t>
+          <t>13058.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>21902.1</v>
+        <v>18823.32</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-413</t>
+          <t>-951</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-832.7079709717071</t>
+          <t>-836.8273699700007</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-800.706105186071</t>
+          <t>-859.4840644606156</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-21.95</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-8.50</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>46.02999999999999</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>48.99</v>
+        <v>48.87</v>
       </c>
       <c r="AN19" t="n">
-        <v>51.52</v>
+        <v>51.33</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-24.50</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-140.30</t>
+          <t>-141.95</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>11302</v>
+        <v>12674.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12352.4</t>
+          <t>13088.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>23372.88</v>
+        <v>21902.1</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1050</t>
+          <t>-413</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-838.5264920236409</t>
+          <t>-832.7079709717071</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1024.462373894361</t>
+          <t>-800.706105186071</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.02999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>49.16</v>
+        <v>48.99</v>
       </c>
       <c r="AN20" t="n">
-        <v>51.72</v>
+        <v>51.52</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-29.79</t>
+          <t>-24.50</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-137.83</t>
+          <t>-140.30</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
@@ -8853,30 +8853,30 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>12214.6</t>
+          <t>12352.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>23633.42</v>
+        <v>23372.88</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-1050</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-804.7199680471464</t>
+          <t>-838.5264920236409</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1331.954815838546</t>
+          <t>-1024.462373894361</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>49.36</v>
+        <v>49.16</v>
       </c>
       <c r="AN21" t="n">
-        <v>51.92</v>
+        <v>51.72</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-35.65</t>
+          <t>-29.79</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>12677.4</v>
+        <v>11302</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>24098.68</v>
+        <v>23633.42</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,17 +9614,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>49.62</v>
+        <v>49.36</v>
       </c>
       <c r="AN22" t="n">
-        <v>52.16</v>
+        <v>51.92</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-35.65</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>14010.2</v>
+        <v>12677.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>24459.88</v>
+        <v>24098.68</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-18.86</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,54 +10044,54 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>49.81</v>
+        <v>49.62</v>
       </c>
       <c r="AN23" t="n">
-        <v>52.35</v>
+        <v>52.16</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,17 +10100,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-35.50</t>
+          <t>-30.34</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.89</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>98901.64133522726</t>
+          <t>98771.73617021277</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>13502.2</v>
+        <v>14010.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>18498.9</t>
+          <t>16688.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>25275.3</v>
+        <v>24459.88</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-4996</t>
+          <t>-2678</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-636.4915067586373</t>
+          <t>-685.0056887100517</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1059.740935176555</t>
+          <t>-951.8336894428303</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>7457.0</t>
+          <t>14018.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>147.26</t>
+          <t>148.06</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>價_量;【d1】;【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69.002</t>
+          <t>39.351</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,84 +898,84 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>30.40</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>17.37</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1032,29 +1032,25 @@
           <t>70.83</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
+      <c r="AH2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.38</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -1065,23 +1061,19 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>102.58</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
+          <t>121.42</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.36</t>
+          <t>-101.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1735650.0</t>
+          <t>990705.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1200790.2</v>
+        <v>1272493.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1023092.8</t>
+          <t>975805.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1253611.68</v>
+        <v>1255709.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>177697</t>
+          <t>296687</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-24563.99529278192</t>
+          <t>-24110.80423351967</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-4253.017188835191</t>
+          <t>-21618.25340757729</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1735650.0</t>
+          <t>990705.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1258,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.098</t>
+          <t>69.002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>17.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,37 +1441,33 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>69.12</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
+          <t>70.83</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.42</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1491,27 +1479,23 @@
         <v>24.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>25.13</v>
+        <v>25.12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>75.35</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
+          <t>102.58</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.97</t>
+          <t>-102.36</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1209308.0</t>
+          <t>1735650.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1015812.4</v>
+        <v>1200790.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>889290.3</t>
+          <t>1023092.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1235178.18</v>
+        <v>1253611.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>126522</t>
+          <t>177697</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-28256.90040259043</t>
+          <t>-24563.99529278192</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-59109.17911960254</t>
+          <t>-4253.017188835191</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1209308.0</t>
+          <t>1735650.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>25.1</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.241</t>
+          <t>48.098</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,69 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
+          <t>69.12</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.44</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN4" t="n">
-        <v>25.14</v>
+        <v>25.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>61.49</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
+          <t>75.35</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.04</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.53</t>
+          <t>-102.97</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1033147.0</t>
+          <t>1209308.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>877200.6</v>
+        <v>1015812.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1117792.0</t>
+          <t>889290.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1238747.06</v>
+        <v>1235178.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-240591</t>
+          <t>126522</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-22647.3951813155</t>
+          <t>-28256.90040259043</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-78970.29690928431</t>
+          <t>-59109.17911960254</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1033147.0</t>
+          <t>1209308.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,17 +2107,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>55.296</t>
+          <t>41.241</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2208,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,69 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>90.2</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
+          <t>75.49</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.43</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.98</v>
+        <v>24.97</v>
       </c>
       <c r="AN5" t="n">
-        <v>25.15</v>
+        <v>25.14</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>65.81</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
+          <t>61.49</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.05</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.07</t>
+          <t>-103.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>802395.6</v>
+        <v>877200.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1119901.0</t>
+          <t>1117792.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1231337.2</v>
+        <v>1238747.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-317505</t>
+          <t>-240591</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12406.86759441208</t>
+          <t>-22647.3951813155</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-85648.56171921245</t>
+          <t>-78970.29690928431</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,99 +2571,99 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>55.296</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>25.101</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-28.35</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-54.87</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,12 +2707,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>94.12</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2752,29 +2720,25 @@
           <t>90.2</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
+      <c r="AH6" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -2785,23 +2749,19 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>62.30</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
+          <t>65.81</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.06</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.74</t>
+          <t>-104.07</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>679118.4</v>
+        <v>802395.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1504911.4</t>
+          <t>1119901.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1211030.44</v>
+        <v>1231337.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-825792</t>
+          <t>-317505</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>909.8040646425397</t>
+          <t>-12406.86759441208</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-130756.0271005662</t>
+          <t>-85648.56171921245</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,22 +2891,22 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,7 +2946,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2996,12 +2956,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32.268</t>
+          <t>25.101</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-47.63</t>
+          <t>-54.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3129,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,32 +3139,28 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>92.16</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
+          <t>90.2</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.34</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM7" t="n">
@@ -3215,23 +3171,19 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>44.98</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
+          <t>62.30</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.06</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-104.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>845395.4</v>
+        <v>679118.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1614180.5</t>
+          <t>1504911.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1212910.14</v>
+        <v>1211030.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-768785</t>
+          <t>-825792</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>24849.04609468049</t>
+          <t>909.8040646425397</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-108939.7623917658</t>
+          <t>-130756.0271005662</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3453,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>32.268</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-52.42</t>
+          <t>-47.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,69 +3551,61 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>94.12</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>78.43</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>92.16</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.14</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN8" t="n">
         <v>25.15</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>44.98</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.09</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>762768.2</v>
+        <v>845395.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1603074.3</t>
+          <t>1614180.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1210877.9</v>
+        <v>1212910.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-840306</t>
+          <t>-768785</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>49174.2840013071</t>
+          <t>24849.04609468049</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-93015.5712937736</t>
+          <t>-108939.7623917658</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-52.42</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,42 +3973,38 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>70.59</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
+          <t>78.43</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.05</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM9" t="n">
@@ -4075,23 +4015,19 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.64</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.09</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1358383.4</v>
+        <v>762768.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1676940.9</t>
+          <t>1603074.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1212587.6</v>
+        <v>1210877.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-318557</t>
+          <t>-840306</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>75026.98496404906</t>
+          <t>49174.2840013071</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-35389.88503614976</t>
+          <t>-93015.5712937736</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,7 +4212,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4286,12 +4222,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4311,11 +4247,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>6606</t>
@@ -4323,12 +4255,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31.352</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4270,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,102 +4280,102 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-19.00</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-15.67</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,69 +4391,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>62.75</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
+          <t>70.59</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.51</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>24.96</v>
+        <v>24.97</v>
       </c>
       <c r="AN10" t="n">
         <v>25.15</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-21.77</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
+          <t>12.64</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.09</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4454,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4464,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1437406.4</v>
+        <v>1358383.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1217210.96</v>
+        <v>1212587.6</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4520,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4565,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4575,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4590,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4605,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4635,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4677,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4692,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4702,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4712,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4777,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4787,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,37 +4813,33 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>45.1</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
+          <t>62.75</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.95</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4928,10 +4848,10 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>24.98</v>
+        <v>24.96</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.16</v>
+        <v>25.15</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,18 +4860,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-29.65</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
+          <t>-21.77</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.09</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4876,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4886,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2330704.4</v>
+        <v>1437406.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1227934.96</v>
+        <v>1217210.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4942,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4987,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5002,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5012,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5027,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5052,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5099,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16.003</t>
+          <t>58.578</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5114,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5124,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5134,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>35.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5199,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5209,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,69 +5235,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>25.49</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.03</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>25</v>
+        <v>24.98</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.17</v>
+        <v>25.16</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-45.60</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>-29.65</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.09</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5298,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.85</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5308,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11768708.92694064</t>
+          <t>11753081.79711246</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2382965.6</v>
+        <v>2330704.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1642914.0</t>
+          <t>1713946.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1217959.22</v>
+        <v>1227934.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>104563.2424099026</t>
+          <t>106414.4436130346</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>158481.2602790978</t>
+          <t>116596.0502302607</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>397625.0</t>
+          <t>1463575.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5364,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5409,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5419,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5434,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5449,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5474,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5601,11 +5509,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>4503</t>
@@ -5613,12 +5517,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>239.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5532,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5547,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-35.04</t>
+          <t>-20.22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5617,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-20.18</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5627,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,74 +5648,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-3.15</t>
-        </is>
+          <t>14.47</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-3.07</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>45.70999999999999</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>47.52</v>
+        <v>47.16</v>
       </c>
       <c r="AN13" t="n">
-        <v>50.15</v>
+        <v>49.93</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-1.35</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5820,7 +5716,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-142.47</t>
+          <t>-142.20</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5726,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4879.0</t>
+          <t>10919.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>5824.2</v>
+        <v>6892.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8965.9</t>
+          <t>8639.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>15289.9</v>
+        <v>14994.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3141</t>
+          <t>-1746</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-1278.792913751238</t>
+          <t>-1298.762116422383</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1866.588918974714</t>
+          <t>-1408.592731113678</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>4879.0</t>
+          <t>10919.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5782,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-24.26</t>
+          <t>-24.92</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,17 +5827,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5956,7 +5852,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5867,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5892,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6031,11 +5927,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>4503</t>
@@ -6043,12 +5935,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +5950,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +5960,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-35.04</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6035,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6045,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,74 +6066,66 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>31.16</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-1.40</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-3.25</t>
-        </is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-3.15</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.02</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>47.86</v>
+        <v>47.52</v>
       </c>
       <c r="AN14" t="n">
-        <v>50.34</v>
+        <v>50.15</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-0.36</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-1.36</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6250,7 +6134,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-142.70</t>
+          <t>-142.47</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6144,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4019.0</t>
+          <t>4879.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>7084.8</v>
+        <v>5824.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9879.8</t>
+          <t>8965.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>15702.14</v>
+        <v>15289.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2794</t>
+          <t>-3141</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-1171.920912801515</t>
+          <t>-1278.792913751238</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1807.062440241383</t>
+          <t>-1866.588918974714</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>4019.0</t>
+          <t>4879.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6200,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-24.26</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6245,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6270,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6285,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6310,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>46.4</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>45.9</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6357,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6382,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6467,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6488,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,59 +6503,51 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>51.45</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-3.39</t>
-        </is>
+          <t>31.16</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-3.25</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>48.12</v>
+        <v>47.86</v>
       </c>
       <c r="AN15" t="n">
-        <v>50.56</v>
+        <v>50.34</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.18</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-1.36</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6680,7 +6556,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-142.66</t>
+          <t>-142.70</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6566,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>5020.0</t>
+          <t>4019.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>9145.200000000001</v>
+        <v>7084.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>10223.6</t>
+          <t>9879.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>16628.22</v>
+        <v>15702.14</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1078</t>
+          <t>-2794</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1056.440635085176</t>
+          <t>-1171.920912801515</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1565.343812042289</t>
+          <t>-1807.062440241383</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>5020.0</t>
+          <t>4019.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,7 +6667,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6816,7 +6692,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6707,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,17 +6732,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6779,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6794,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6804,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +6879,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +6889,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,74 +6910,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>70.42</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-3.79</t>
-        </is>
+          <t>51.45</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-3.39</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>48.36</v>
+        <v>48.12</v>
       </c>
       <c r="AN16" t="n">
-        <v>50.76</v>
+        <v>50.56</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>53.18</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-1.36</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -7110,7 +6978,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.66</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +6988,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>11051</v>
+        <v>9145.200000000001</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11176.5</t>
+          <t>10223.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>17175.12</v>
+        <v>16628.22</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-125</t>
+          <t>-1078</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-963.9127847293369</t>
+          <t>-1056.440635085176</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1271.376349899216</t>
+          <t>-1565.343812042289</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7044,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7089,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7099,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7114,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7129,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7154,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7191,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7201,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7216,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7226,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7301,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7311,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,74 +7332,66 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>77.15</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-4.28</t>
-        </is>
+          <t>70.42</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-3.79</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>48.64</v>
+        <v>48.36</v>
       </c>
       <c r="AN17" t="n">
-        <v>50.95</v>
+        <v>50.76</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-1.36</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7540,7 +7400,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-142.51</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7410,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>10386.2</v>
+        <v>11051</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>11531.8</t>
+          <t>11176.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>17989.48</v>
+        <v>17175.12</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1145</t>
+          <t>-125</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-908.0103183348134</t>
+          <t>-963.9127847293369</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1299.516534341283</t>
+          <t>-1271.376349899216</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>5577.0</t>
+          <t>9626.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7466,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7511,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7521,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7536,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7551,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7576,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7751,11 +7611,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>4503</t>
@@ -7763,12 +7619,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7634,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7644,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7719,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7729,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,74 +7750,66 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>53.74</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-5.40</t>
-        </is>
+          <t>77.15</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-4.28</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="AN18" t="n">
-        <v>51.13</v>
+        <v>50.95</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>53.47</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-5.74</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-1.44</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-1.36</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7970,7 +7818,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.51</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7828,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>12107.6</v>
+        <v>10386.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13058.9</t>
+          <t>11531.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>18823.32</v>
+        <v>17989.48</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-951</t>
+          <t>-1145</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-836.8273699700007</t>
+          <t>-908.0103183348134</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-859.4840644606156</t>
+          <t>-1299.516534341283</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>11182.0</t>
+          <t>5577.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +7884,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-21.95</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +7929,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +7939,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +7954,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +7969,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +7994,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8041,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8056,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8066,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8141,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8151,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,74 +8172,66 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>31.63</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-5.67</t>
-        </is>
+          <t>53.74</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-5.4</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>48.87</v>
+        <v>48.78</v>
       </c>
       <c r="AN19" t="n">
-        <v>51.33</v>
+        <v>51.13</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-15.76</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-1.34</t>
-        </is>
+          <t>-5.74</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-1.36</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8400,7 +8240,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-141.95</t>
+          <t>-142.56</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8250,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>12674.8</v>
+        <v>12107.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>13088.5</t>
+          <t>13058.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>21902.1</v>
+        <v>18823.32</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-413</t>
+          <t>-951</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-832.7079709717071</t>
+          <t>-836.8273699700007</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-800.706105186071</t>
+          <t>-859.4840644606156</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>14321.0</t>
+          <t>11182.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8306,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-21.95</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8351,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8376,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8391,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8416,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>46.0</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8463,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8478,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8488,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-8.50</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8563,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8573,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,74 +8594,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>12.59</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-6.05</t>
-        </is>
+          <t>31.63</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-5.67</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>46.02999999999999</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>48.99</v>
+        <v>48.87</v>
       </c>
       <c r="AN20" t="n">
-        <v>51.52</v>
+        <v>51.33</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-24.50</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-1.60</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
+          <t>-15.76</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-1.34</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8830,7 +8662,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-140.30</t>
+          <t>-141.95</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8672,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>11302</v>
+        <v>12674.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>12352.4</t>
+          <t>13088.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>23372.88</v>
+        <v>21902.1</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1050</t>
+          <t>-413</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-838.5264920236409</t>
+          <t>-832.7079709717071</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1024.462373894361</t>
+          <t>-800.706105186071</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>14549.0</t>
+          <t>14321.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8728,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8773,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8798,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8813,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,7 +8838,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -9016,12 +8848,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +8885,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +8900,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +8910,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.50</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +8985,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-19.30</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +8995,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,74 +9016,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>11.68</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-5.97</t>
-        </is>
+          <t>12.59</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-6.05</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>46.02999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>49.16</v>
+        <v>48.99</v>
       </c>
       <c r="AN21" t="n">
-        <v>51.72</v>
+        <v>51.52</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-29.79</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-1.21</t>
-        </is>
+          <t>-24.50</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-1.29</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9260,7 +9084,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-137.83</t>
+          <t>-140.30</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,12 +9094,12 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
@@ -9283,30 +9107,30 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>12214.6</t>
+          <t>12352.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>23633.42</v>
+        <v>23372.88</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-912</t>
+          <t>-1050</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-804.7199680471464</t>
+          <t>-838.5264920236409</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1331.954815838546</t>
+          <t>-1024.462373894361</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>6302.0</t>
+          <t>14549.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9150,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9195,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9205,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9220,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9235,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9260,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9307,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9322,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9332,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9407,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-19.30</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9417,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,74 +9438,66 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5.39</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>-3.35</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-5.66</t>
-        </is>
+          <t>11.68</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-5.97</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>49.36</v>
+        <v>49.16</v>
       </c>
       <c r="AN22" t="n">
-        <v>51.92</v>
+        <v>51.72</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>53.77</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-35.65</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-1.52</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
+          <t>-29.79</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>-1.21</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9690,7 +9506,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-135.01</t>
+          <t>-137.83</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9516,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>12677.4</v>
+        <v>11302</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14056.7</t>
+          <t>12214.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>24098.68</v>
+        <v>23633.42</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1379</t>
+          <t>-912</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-708.8590866305283</t>
+          <t>-804.7199680471464</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-840.0527751931495</t>
+          <t>-1331.954815838546</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>14184.0</t>
+          <t>6302.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9572,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-25.74</t>
+          <t>-24.09</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9617,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9627,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9642,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9657,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9682,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9729,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>297.0</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9744,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9754,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +9829,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-17.46</t>
+          <t>-21.05</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +9839,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,17 +9860,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10062,56 +9878,48 @@
           <t>5.39</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-5.04</t>
-        </is>
+      <c r="AH23" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-5.66</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>46.56</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>49.62</v>
+        <v>49.36</v>
       </c>
       <c r="AN23" t="n">
-        <v>52.16</v>
+        <v>51.92</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-30.34</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
+          <t>-35.65</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>-1.12</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -10120,7 +9928,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-131.89</t>
+          <t>-135.01</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +9938,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>98771.73617021277</t>
+          <t>98655.03186968839</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>14010.2</v>
+        <v>12677.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>16688.8</t>
+          <t>14056.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>24459.88</v>
+        <v>24098.68</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2678</t>
+          <t>-1379</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-685.0056887100517</t>
+          <t>-708.8590866305283</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-951.8336894428303</t>
+          <t>-840.0527751931495</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>14018.0</t>
+          <t>14184.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +9994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-25.74</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10039,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10049,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10064,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>148.06</t>
+          <t>146.77</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10079,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10104,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/自動販賣機.xlsx
+++ b/Result/checksun_type/自動販賣機.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39.351</t>
+          <t>24.764</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>24.98</v>
+        <v>25</v>
       </c>
       <c r="AN2" t="n">
         <v>25.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>121.42</t>
+          <t>232.54</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.02</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.81</t>
+          <t>-101.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>990705.0</t>
+          <t>622692.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1272493.2</v>
+        <v>1118300.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>975805.8</t>
+          <t>960348.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1255709.64</v>
+        <v>1220304.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>296687</t>
+          <t>157952</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-24110.80423351967</t>
+          <t>-29760.59395536395</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-21618.25340757729</t>
+          <t>-60834.43742550747</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>990705.0</t>
+          <t>622692.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,22 +1203,22 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>11.88</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>69.002</t>
+          <t>39.351</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,84 +1320,84 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30.40</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>17.37</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,17 +1436,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1455,24 +1455,24 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -1483,19 +1483,19 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>102.58</t>
+          <t>121.42</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.36</t>
+          <t>-101.81</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1735650.0</t>
+          <t>990705.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1200790.2</v>
+        <v>1272493.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1023092.8</t>
+          <t>975805.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1253611.68</v>
+        <v>1255709.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>177697</t>
+          <t>296687</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-24563.99529278192</t>
+          <t>-24110.80423351967</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-4253.017188835191</t>
+          <t>-21618.25340757729</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1735650.0</t>
+          <t>990705.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1675,17 +1675,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,42 +1727,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>69.002</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>48.098</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>25.1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>17.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,38 +1858,38 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1901,23 +1901,23 @@
         <v>24.98</v>
       </c>
       <c r="AN4" t="n">
-        <v>25.13</v>
+        <v>25.12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>75.35</t>
+          <t>102.58</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.97</t>
+          <t>-102.36</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1209308.0</t>
+          <t>1735650.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1015812.4</v>
+        <v>1200790.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>889290.3</t>
+          <t>1023092.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1235178.18</v>
+        <v>1253611.68</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>126522</t>
+          <t>177697</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-28256.90040259043</t>
+          <t>-24563.99529278192</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-59109.17911960254</t>
+          <t>-4253.017188835191</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1209308.0</t>
+          <t>1735650.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>25.1</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.241</t>
+          <t>48.098</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-21.52</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>75.49</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.32</v>
+        <v>0.04</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>25.14</v>
+        <v>25.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>61.49</t>
+          <t>75.35</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.53</t>
+          <t>-102.97</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1033147.0</t>
+          <t>1209308.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>877200.6</v>
+        <v>1015812.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1117792.0</t>
+          <t>889290.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1238747.06</v>
+        <v>1235178.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-240591</t>
+          <t>126522</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-22647.3951813155</t>
+          <t>-28256.90040259043</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-78970.29690928431</t>
+          <t>-59109.17911960254</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1033147.0</t>
+          <t>1209308.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>55.296</t>
+          <t>41.241</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-28.35</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>24.98</v>
+        <v>24.97</v>
       </c>
       <c r="AN6" t="n">
-        <v>25.15</v>
+        <v>25.14</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>65.81</t>
+          <t>61.49</t>
         </is>
       </c>
       <c r="AQ6" t="n">
         <v>-0.02</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.07</t>
+          <t>-103.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>802395.6</v>
+        <v>877200.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1119901.0</t>
+          <t>1117792.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1231337.2</v>
+        <v>1238747.06</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-317505</t>
+          <t>-240591</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12406.86759441208</t>
+          <t>-22647.3951813155</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-85648.56171921245</t>
+          <t>-78970.29690928431</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1393656.0</t>
+          <t>1033147.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2941,27 +2941,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,99 +2993,99 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>55.296</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>25.101</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-28.35</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-54.87</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,17 +3124,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>94.12</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3143,24 +3143,24 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.34</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AM7" t="n">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>65.81</t>
         </is>
       </c>
       <c r="AQ7" t="n">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.74</t>
+          <t>-104.07</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>679118.4</v>
+        <v>802395.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1504911.4</t>
+          <t>1119901.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1211030.44</v>
+        <v>1231337.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-825792</t>
+          <t>-317505</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>909.8040646425397</t>
+          <t>-12406.86759441208</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-130756.0271005662</t>
+          <t>-85648.56171921245</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>632190.0</t>
+          <t>1393656.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,22 +3313,22 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>11.88</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,99 +3415,99 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>25.101</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>32.268</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-54.87</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-47.63</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,28 +3561,28 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.14</v>
+        <v>0.34</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM8" t="n">
@@ -3593,19 +3593,19 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.47</t>
+          <t>-104.74</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>845395.4</v>
+        <v>679118.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1614180.5</t>
+          <t>1504911.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1212910.14</v>
+        <v>1211030.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-768785</t>
+          <t>-825792</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>24849.04609468049</t>
+          <t>909.8040646425397</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-108939.7623917658</t>
+          <t>-130756.0271005662</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>810761.0</t>
+          <t>632190.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3785,22 +3785,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>32.268</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-52.42</t>
+          <t>-47.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>94.12</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="AN9" t="n">
         <v>25.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.09</t>
+          <t>-105.47</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>762768.2</v>
+        <v>845395.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1603074.3</t>
+          <t>1614180.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1210877.9</v>
+        <v>1212910.14</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-840306</t>
+          <t>-768785</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>49174.2840013071</t>
+          <t>24849.04609468049</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-93015.5712937736</t>
+          <t>-108939.7623917658</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>516249.0</t>
+          <t>810761.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4207,27 +4207,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4247,7 +4247,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>6606</t>
@@ -4255,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4270,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4280,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4290,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.00</t>
+          <t>-52.42</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4300,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4355,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4365,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4386,43 +4390,43 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.45</v>
+        <v>0.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.51</v>
+        <v>0.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AM10" t="n">
@@ -4433,20 +4437,20 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AQ10" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AR10" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AR10" t="n">
-        <v>-0.09</v>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -4454,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.09</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4464,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1358383.4</v>
+        <v>762768.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1676940.9</t>
+          <t>1603074.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1212587.6</v>
+        <v>1210877.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-318557</t>
+          <t>-840306</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>75026.98496404906</t>
+          <t>49174.2840013071</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-35389.88503614976</t>
+          <t>-93015.5712937736</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>659122.0</t>
+          <t>516249.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4520,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4545,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4565,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4590,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4605,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4625,12 +4629,12 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4640,12 +4644,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4667,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4677,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31.352</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4692,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4702,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4712,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>-19.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4722,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4777,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4787,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4808,63 +4812,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.32</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.95</v>
+        <v>-0.51</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>24.96</v>
+        <v>24.97</v>
       </c>
       <c r="AN11" t="n">
         <v>25.15</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="AR11" t="n">
         <v>-0.09</v>
@@ -4876,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.68</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4886,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1437406.4</v>
+        <v>1358383.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1704496.9</t>
+          <t>1676940.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1217210.96</v>
+        <v>1212587.6</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-267090</t>
+          <t>-318557</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>95102.77950953975</t>
+          <t>75026.98496404906</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>32888.62694031815</t>
+          <t>-35389.88503614976</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>777270.0</t>
+          <t>659122.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4942,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4967,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4987,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4997,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5012,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5027,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5047,7 +5051,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5057,17 +5061,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5099,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>58.578</t>
+          <t>31.352</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5114,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5124,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5134,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5144,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5199,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5209,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5230,38 +5234,38 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.03</v>
+        <v>-0.95</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5270,10 +5274,10 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>24.98</v>
+        <v>24.96</v>
       </c>
       <c r="AN12" t="n">
-        <v>25.16</v>
+        <v>25.15</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5282,7 +5286,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-21.77</t>
         </is>
       </c>
       <c r="AQ12" t="n">
@@ -5298,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-106.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5308,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>11753081.79711246</t>
+          <t>11736664.43171472</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2330704.4</v>
+        <v>1437406.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1713946.5</t>
+          <t>1704496.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1227934.96</v>
+        <v>1217210.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>616757</t>
+          <t>-267090</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>106414.4436130346</t>
+          <t>95102.77950953975</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>116596.0502302607</t>
+          <t>32888.62694031815</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1463575.0</t>
+          <t>777270.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5364,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5389,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5409,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5424,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5434,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5449,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5469,27 +5473,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>24.8</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>24.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5509,7 +5513,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>4503</t>
@@ -5517,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>239.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5532,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5547,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-20.22</t>
+          <t>-31.31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5617,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-20.18</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5627,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5648,66 +5656,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-0.46</v>
+        <v>-0.04</v>
       </c>
       <c r="AI13" t="n">
-        <v>-3.07</v>
+        <v>-2.58</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>45.70999999999999</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>47.16</v>
+        <v>46.88</v>
       </c>
       <c r="AN13" t="n">
-        <v>49.93</v>
+        <v>49.71</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>52.72</t>
+          <t>52.55</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>-1.31</v>
+        <v>-1.27</v>
       </c>
       <c r="AR13" t="n">
-        <v>-1.35</v>
+        <v>-1.33</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5716,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-142.20</t>
+          <t>-141.73</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5726,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>98655.03186968839</t>
+          <t>98524.12234794907</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>10919.0</t>
+          <t>4068.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>6892.6</v>
+        <v>5781</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8639.4</t>
+          <t>8416.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>14994.42</v>
+        <v>14571.56</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1746</t>
+          <t>-2635</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-1298.762116422383</t>
+          <t>-1339.968803331726</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1408.592731113678</t>
+          <t>-1566.60558133311</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>10919.0</t>
+          <t>4068.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5782,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-24.92</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5827,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5837,7 +5845,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5852,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>146.77</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5867,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5892,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5927,7 +5935,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>4503</t>
@@ -5935,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>239.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5950,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5960,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-35.04</t>
+          <t>-20.22</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6035,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-20.18</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6045,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6066,66 +6078,66 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-0.26</v>
+        <v>-0.46</v>
       </c>
       <c r="AI14" t="n">
-        <v>-3.15</v>
+        <v>-3.07</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-5.20</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>45.70999999999999</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>47.52</v>
+        <v>47.16</v>
       </c>
       <c r="AN14" t="n">
-        <v>50.15</v>
+        <v>49.93</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.72</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>-1.33</v>
+        <v>-1.31</v>
       </c>
       <c r="AR14" t="n">
-        <v>-1.36</v>
+        <v>-1.35</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6134,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-142.47</t>
+          <t>-142.20</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6144,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>98655.03186968839</t>
+          <t>98524.12234794907</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4879.0</t>
+          <t>10919.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>5824.2</v>
+        <v>6892.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>8965.9</t>
+          <t>8639.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>15289.9</v>
+        <v>14994.42</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3141</t>
+          <t>-1746</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-1278.792913751238</t>
+          <t>-1298.762116422383</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1866.588918974714</t>
+          <t>-1408.592731113678</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>4879.0</t>
+          <t>10919.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6200,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-24.26</t>
+          <t>-24.92</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6245,17 +6257,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6270,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>146.77</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6285,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6310,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6347,7 +6359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6357,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6372,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6382,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-28.29</t>
+          <t>-35.04</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6457,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6467,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6488,63 +6500,63 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>31.16</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>-1.4</v>
+        <v>-0.26</v>
       </c>
       <c r="AI15" t="n">
-        <v>-3.25</v>
+        <v>-3.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.02</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>47.86</v>
+        <v>47.52</v>
       </c>
       <c r="AN15" t="n">
-        <v>50.34</v>
+        <v>50.15</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-1.37</v>
+        <v>-1.33</v>
       </c>
       <c r="AR15" t="n">
         <v>-1.36</v>
@@ -6556,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-142.70</t>
+          <t>-142.47</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6566,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>98655.03186968839</t>
+          <t>98524.12234794907</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4019.0</t>
+          <t>4879.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>7084.8</v>
+        <v>5824.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9879.8</t>
+          <t>8965.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>15702.14</v>
+        <v>15289.9</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2794</t>
+          <t>-3141</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1171.920912801515</t>
+          <t>-1278.792913751238</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1807.062440241383</t>
+          <t>-1866.588918974714</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>4019.0</t>
+          <t>4879.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6622,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-24.26</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6667,17 +6679,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6692,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>146.77</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6707,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6732,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>46.4</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>45.9</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6779,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6804,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-28.29</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6889,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6910,12 +6922,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -6925,48 +6937,48 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>51.45</t>
+          <t>31.16</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>-1.81</v>
+        <v>-1.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>-3.39</v>
+        <v>-3.25</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>48.12</v>
+        <v>47.86</v>
       </c>
       <c r="AN16" t="n">
-        <v>50.56</v>
+        <v>50.34</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>53.18</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>-1.38</v>
+        <v>-1.37</v>
       </c>
       <c r="AR16" t="n">
         <v>-1.36</v>
@@ -6978,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-142.66</t>
+          <t>-142.70</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -6988,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>98655.03186968839</t>
+          <t>98524.12234794907</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>5020.0</t>
+          <t>4019.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>9145.200000000001</v>
+        <v>7084.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>10223.6</t>
+          <t>9879.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>16628.22</v>
+        <v>15702.14</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1078</t>
+          <t>-2794</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-1056.440635085176</t>
+          <t>-1171.920912801515</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1565.343812042289</t>
+          <t>-1807.062440241383</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>5020.0</t>
+          <t>4019.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7089,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7114,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>146.77</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7129,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7154,17 +7166,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7201,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7216,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7226,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7301,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7311,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7332,63 +7344,63 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>51.45</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-1.46</v>
+        <v>-1.81</v>
       </c>
       <c r="AI17" t="n">
-        <v>-3.79</v>
+        <v>-3.39</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>48.36</v>
+        <v>48.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>50.76</v>
+        <v>50.56</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>53.18</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>-1.36</v>
+        <v>-1.38</v>
       </c>
       <c r="AR17" t="n">
         <v>-1.36</v>
@@ -7400,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-142.56</t>
+          <t>-142.66</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7410,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>98655.03186968839</t>
+          <t>98524.12234794907</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>11051</v>
+        <v>9145.200000000001</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>11176.5</t>
+          <t>10223.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>17175.12</v>
+        <v>16628.22</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-125</t>
+          <t>-1078</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-963.9127847293369</t>
+          <t>-1056.440635085176</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1271.376349899216</t>
+          <t>-1565.343812042289</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>9626.0</t>
+          <t>5020.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7466,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7511,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7521,7 +7533,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7536,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>146.77</t>
+          <t>147.26</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7551,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7576,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>45.65</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7611,7 +7623,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>4503</t>
@@ -7619,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7634,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7644,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t